--- a/activitereelgueudet.xlsx
+++ b/activitereelgueudet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B745491-837C-4857-931C-51630D74D972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15122314-25CD-4127-8DA3-0B1D881235E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2671" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4252" uniqueCount="532">
   <si>
     <t>codePlaque</t>
   </si>
@@ -1239,6 +1239,396 @@
   </si>
   <si>
     <t>Février</t>
+  </si>
+  <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>22.48</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>18.1</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>24.29</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>28.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84713 12                 </t>
+  </si>
+  <si>
+    <t>84713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLATE FORME                   </t>
+  </si>
+  <si>
+    <t>215.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84720 12                 </t>
+  </si>
+  <si>
+    <t>84720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIROIR + VENTOUSE             </t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84954 22                 </t>
+  </si>
+  <si>
+    <t>84954</t>
+  </si>
+  <si>
+    <t>LUSTRANT SHOWROOM GLAZE + PULV</t>
+  </si>
+  <si>
+    <t>13.17</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85385 22                 </t>
+  </si>
+  <si>
+    <t>85385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBAN MASQUAGE 10 X 50 MM     </t>
+  </si>
+  <si>
+    <t>17.43</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>39.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85387 22                 </t>
+  </si>
+  <si>
+    <t>85387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBAN MOUSSE RACCORD NOYE     </t>
+  </si>
+  <si>
+    <t>15.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85987 10                 </t>
+  </si>
+  <si>
+    <t>85987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BODY FINISH PAINT GRIS 500ML  </t>
+  </si>
+  <si>
+    <t>9.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86037 00                 </t>
+  </si>
+  <si>
+    <t>86037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGRAFES PLATES ST16 - 6MM     </t>
+  </si>
+  <si>
+    <t>18.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86039 00                 </t>
+  </si>
+  <si>
+    <t>86039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGRAFES ONDULEES ST26 - 6 MM  </t>
+  </si>
+  <si>
+    <t>18.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86040 00                 </t>
+  </si>
+  <si>
+    <t>86040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGRAFES ONDULEES ST28 - 8 MM  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86041 00                 </t>
+  </si>
+  <si>
+    <t>86041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGRAFES ANGULAIRES ST38-8MM   </t>
+  </si>
+  <si>
+    <t>6.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86280 00                 </t>
+  </si>
+  <si>
+    <t>86280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGRAFES W ST 78 - 8 MM        </t>
+  </si>
+  <si>
+    <t>18.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86358 00                 </t>
+  </si>
+  <si>
+    <t>86358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGRAFES LARGES EN W           </t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>12.79</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>923664</t>
+  </si>
+  <si>
+    <t>PONT-AUDEMER</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>30.65</t>
+  </si>
+  <si>
+    <t>16.85</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86472 22                 </t>
+  </si>
+  <si>
+    <t>86472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESODORISANT CRANBERRY        </t>
+  </si>
+  <si>
+    <t>13.15</t>
+  </si>
+  <si>
+    <t>8.03</t>
+  </si>
+  <si>
+    <t>19.37</t>
+  </si>
+  <si>
+    <t>21.22</t>
+  </si>
+  <si>
+    <t>8.72</t>
+  </si>
+  <si>
+    <t>19.25</t>
+  </si>
+  <si>
+    <t>5.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87000 28                 </t>
+  </si>
+  <si>
+    <t>87000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBBER GUARD                  </t>
+  </si>
+  <si>
+    <t>20.14</t>
+  </si>
+  <si>
+    <t>14.55</t>
+  </si>
+  <si>
+    <t>14.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87070 02                 </t>
+  </si>
+  <si>
+    <t>87070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT SUPER BOND                </t>
+  </si>
+  <si>
+    <t>28.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1188 33                 </t>
+  </si>
+  <si>
+    <t>A1188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD2 DISQUES EPONGES SUPERFINS </t>
+  </si>
+  <si>
+    <t>20.45</t>
+  </si>
+  <si>
+    <t>27.77</t>
+  </si>
+  <si>
+    <t>27.65</t>
+  </si>
+  <si>
+    <t>27.74</t>
+  </si>
+  <si>
+    <t>27.66</t>
+  </si>
+  <si>
+    <t>27.58</t>
+  </si>
+  <si>
+    <t>27.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1301 33                 </t>
+  </si>
+  <si>
+    <t>A1301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISQUES DURALITE 150MM P2000  </t>
+  </si>
+  <si>
+    <t>30.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1347 33                 </t>
+  </si>
+  <si>
+    <t>A1347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINECUT P3000 150 MM          </t>
+  </si>
+  <si>
+    <t>30.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1351 33                 </t>
+  </si>
+  <si>
+    <t>A1351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERFACE FINECUT MEDIUM 5MM  </t>
+  </si>
+  <si>
+    <t>7.41</t>
+  </si>
+  <si>
+    <t>26.34</t>
+  </si>
+  <si>
+    <t>21.8</t>
+  </si>
+  <si>
+    <t>21.86</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>21.88</t>
+  </si>
+  <si>
+    <t>12.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0109 00                 </t>
+  </si>
+  <si>
+    <t>E0109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSE CORDE A PIANO           </t>
+  </si>
+  <si>
+    <t>36.45</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>11.14</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>10.5</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
+    <t>10.54</t>
+  </si>
+  <si>
+    <t>Mars</t>
   </si>
 </sst>
 </file>
@@ -1610,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E505DD-DFE7-49B0-9B59-53447E0B5813}">
-  <dimension ref="A1:S157"/>
+  <dimension ref="A1:S250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
@@ -10873,6 +11263,5493 @@
         <v>401</v>
       </c>
       <c r="S157">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>206</v>
+      </c>
+      <c r="B158" t="s">
+        <v>207</v>
+      </c>
+      <c r="C158" t="s">
+        <v>212</v>
+      </c>
+      <c r="D158" t="s">
+        <v>213</v>
+      </c>
+      <c r="E158" t="s">
+        <v>214</v>
+      </c>
+      <c r="F158" t="s">
+        <v>70</v>
+      </c>
+      <c r="G158" t="s">
+        <v>402</v>
+      </c>
+      <c r="H158" t="s">
+        <v>88</v>
+      </c>
+      <c r="I158" t="s">
+        <v>89</v>
+      </c>
+      <c r="J158">
+        <v>22.48</v>
+      </c>
+      <c r="K158" t="s">
+        <v>23</v>
+      </c>
+      <c r="L158" t="s">
+        <v>403</v>
+      </c>
+      <c r="M158" t="s">
+        <v>18</v>
+      </c>
+      <c r="N158" t="s">
+        <v>19</v>
+      </c>
+      <c r="O158" t="s">
+        <v>20</v>
+      </c>
+      <c r="P158" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>404</v>
+      </c>
+      <c r="R158" t="s">
+        <v>531</v>
+      </c>
+      <c r="S158">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>206</v>
+      </c>
+      <c r="B159" t="s">
+        <v>207</v>
+      </c>
+      <c r="C159" t="s">
+        <v>251</v>
+      </c>
+      <c r="D159" t="s">
+        <v>252</v>
+      </c>
+      <c r="E159" t="s">
+        <v>198</v>
+      </c>
+      <c r="F159" t="s">
+        <v>119</v>
+      </c>
+      <c r="G159" t="s">
+        <v>405</v>
+      </c>
+      <c r="H159" t="s">
+        <v>168</v>
+      </c>
+      <c r="I159" t="s">
+        <v>169</v>
+      </c>
+      <c r="J159">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="K159" t="s">
+        <v>23</v>
+      </c>
+      <c r="L159" t="s">
+        <v>403</v>
+      </c>
+      <c r="M159" t="s">
+        <v>18</v>
+      </c>
+      <c r="N159" t="s">
+        <v>19</v>
+      </c>
+      <c r="O159" t="s">
+        <v>20</v>
+      </c>
+      <c r="P159" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>406</v>
+      </c>
+      <c r="R159" t="s">
+        <v>531</v>
+      </c>
+      <c r="S159">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>206</v>
+      </c>
+      <c r="B160" t="s">
+        <v>207</v>
+      </c>
+      <c r="C160" t="s">
+        <v>215</v>
+      </c>
+      <c r="D160" t="s">
+        <v>216</v>
+      </c>
+      <c r="E160" t="s">
+        <v>32</v>
+      </c>
+      <c r="F160" t="s">
+        <v>33</v>
+      </c>
+      <c r="G160" t="s">
+        <v>407</v>
+      </c>
+      <c r="H160" t="s">
+        <v>189</v>
+      </c>
+      <c r="I160" t="s">
+        <v>190</v>
+      </c>
+      <c r="J160">
+        <v>24.29</v>
+      </c>
+      <c r="K160" t="s">
+        <v>23</v>
+      </c>
+      <c r="L160" t="s">
+        <v>403</v>
+      </c>
+      <c r="M160" t="s">
+        <v>18</v>
+      </c>
+      <c r="N160" t="s">
+        <v>19</v>
+      </c>
+      <c r="O160" t="s">
+        <v>20</v>
+      </c>
+      <c r="P160" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>408</v>
+      </c>
+      <c r="R160" t="s">
+        <v>531</v>
+      </c>
+      <c r="S160">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>206</v>
+      </c>
+      <c r="B161" t="s">
+        <v>207</v>
+      </c>
+      <c r="C161" t="s">
+        <v>221</v>
+      </c>
+      <c r="D161" t="s">
+        <v>222</v>
+      </c>
+      <c r="E161" t="s">
+        <v>223</v>
+      </c>
+      <c r="F161" t="s">
+        <v>151</v>
+      </c>
+      <c r="G161" t="s">
+        <v>409</v>
+      </c>
+      <c r="H161" t="s">
+        <v>189</v>
+      </c>
+      <c r="I161" t="s">
+        <v>190</v>
+      </c>
+      <c r="J161">
+        <v>24.29</v>
+      </c>
+      <c r="K161" t="s">
+        <v>23</v>
+      </c>
+      <c r="L161" t="s">
+        <v>403</v>
+      </c>
+      <c r="M161" t="s">
+        <v>18</v>
+      </c>
+      <c r="N161" t="s">
+        <v>19</v>
+      </c>
+      <c r="O161" t="s">
+        <v>20</v>
+      </c>
+      <c r="P161" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>408</v>
+      </c>
+      <c r="R161" t="s">
+        <v>531</v>
+      </c>
+      <c r="S161">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>206</v>
+      </c>
+      <c r="B162" t="s">
+        <v>207</v>
+      </c>
+      <c r="C162" t="s">
+        <v>215</v>
+      </c>
+      <c r="D162" t="s">
+        <v>216</v>
+      </c>
+      <c r="E162" t="s">
+        <v>32</v>
+      </c>
+      <c r="F162" t="s">
+        <v>33</v>
+      </c>
+      <c r="G162" t="s">
+        <v>407</v>
+      </c>
+      <c r="H162" t="s">
+        <v>53</v>
+      </c>
+      <c r="I162" t="s">
+        <v>54</v>
+      </c>
+      <c r="J162">
+        <v>56.44</v>
+      </c>
+      <c r="K162" t="s">
+        <v>22</v>
+      </c>
+      <c r="L162" t="s">
+        <v>403</v>
+      </c>
+      <c r="M162" t="s">
+        <v>18</v>
+      </c>
+      <c r="N162" t="s">
+        <v>19</v>
+      </c>
+      <c r="O162" t="s">
+        <v>20</v>
+      </c>
+      <c r="P162" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>410</v>
+      </c>
+      <c r="R162" t="s">
+        <v>531</v>
+      </c>
+      <c r="S162">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>206</v>
+      </c>
+      <c r="B163" t="s">
+        <v>207</v>
+      </c>
+      <c r="C163" t="s">
+        <v>215</v>
+      </c>
+      <c r="D163" t="s">
+        <v>216</v>
+      </c>
+      <c r="E163" t="s">
+        <v>32</v>
+      </c>
+      <c r="F163" t="s">
+        <v>33</v>
+      </c>
+      <c r="G163" t="s">
+        <v>409</v>
+      </c>
+      <c r="H163" t="s">
+        <v>411</v>
+      </c>
+      <c r="I163" t="s">
+        <v>412</v>
+      </c>
+      <c r="J163">
+        <v>215.08</v>
+      </c>
+      <c r="K163" t="s">
+        <v>23</v>
+      </c>
+      <c r="L163" t="s">
+        <v>403</v>
+      </c>
+      <c r="M163" t="s">
+        <v>18</v>
+      </c>
+      <c r="N163" t="s">
+        <v>19</v>
+      </c>
+      <c r="O163" t="s">
+        <v>20</v>
+      </c>
+      <c r="P163" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>414</v>
+      </c>
+      <c r="R163" t="s">
+        <v>531</v>
+      </c>
+      <c r="S163">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>206</v>
+      </c>
+      <c r="B164" t="s">
+        <v>207</v>
+      </c>
+      <c r="C164" t="s">
+        <v>215</v>
+      </c>
+      <c r="D164" t="s">
+        <v>216</v>
+      </c>
+      <c r="E164" t="s">
+        <v>32</v>
+      </c>
+      <c r="F164" t="s">
+        <v>33</v>
+      </c>
+      <c r="G164" t="s">
+        <v>409</v>
+      </c>
+      <c r="H164" t="s">
+        <v>415</v>
+      </c>
+      <c r="I164" t="s">
+        <v>416</v>
+      </c>
+      <c r="J164">
+        <v>28</v>
+      </c>
+      <c r="K164" t="s">
+        <v>23</v>
+      </c>
+      <c r="L164" t="s">
+        <v>403</v>
+      </c>
+      <c r="M164" t="s">
+        <v>18</v>
+      </c>
+      <c r="N164" t="s">
+        <v>19</v>
+      </c>
+      <c r="O164" t="s">
+        <v>20</v>
+      </c>
+      <c r="P164" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>418</v>
+      </c>
+      <c r="R164" t="s">
+        <v>531</v>
+      </c>
+      <c r="S164">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>206</v>
+      </c>
+      <c r="B165" t="s">
+        <v>207</v>
+      </c>
+      <c r="C165" t="s">
+        <v>215</v>
+      </c>
+      <c r="D165" t="s">
+        <v>216</v>
+      </c>
+      <c r="E165" t="s">
+        <v>32</v>
+      </c>
+      <c r="F165" t="s">
+        <v>33</v>
+      </c>
+      <c r="G165" t="s">
+        <v>419</v>
+      </c>
+      <c r="H165" t="s">
+        <v>420</v>
+      </c>
+      <c r="I165" t="s">
+        <v>421</v>
+      </c>
+      <c r="J165">
+        <v>13.17</v>
+      </c>
+      <c r="K165" t="s">
+        <v>23</v>
+      </c>
+      <c r="L165" t="s">
+        <v>403</v>
+      </c>
+      <c r="M165" t="s">
+        <v>18</v>
+      </c>
+      <c r="N165" t="s">
+        <v>19</v>
+      </c>
+      <c r="O165" t="s">
+        <v>20</v>
+      </c>
+      <c r="P165" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>423</v>
+      </c>
+      <c r="R165" t="s">
+        <v>531</v>
+      </c>
+      <c r="S165">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>206</v>
+      </c>
+      <c r="B166" t="s">
+        <v>207</v>
+      </c>
+      <c r="C166" t="s">
+        <v>215</v>
+      </c>
+      <c r="D166" t="s">
+        <v>216</v>
+      </c>
+      <c r="E166" t="s">
+        <v>32</v>
+      </c>
+      <c r="F166" t="s">
+        <v>33</v>
+      </c>
+      <c r="G166" t="s">
+        <v>424</v>
+      </c>
+      <c r="H166" t="s">
+        <v>132</v>
+      </c>
+      <c r="I166" t="s">
+        <v>133</v>
+      </c>
+      <c r="J166">
+        <v>59.22</v>
+      </c>
+      <c r="K166" t="s">
+        <v>50</v>
+      </c>
+      <c r="L166" t="s">
+        <v>403</v>
+      </c>
+      <c r="M166" t="s">
+        <v>18</v>
+      </c>
+      <c r="N166" t="s">
+        <v>19</v>
+      </c>
+      <c r="O166" t="s">
+        <v>20</v>
+      </c>
+      <c r="P166" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>232</v>
+      </c>
+      <c r="R166" t="s">
+        <v>531</v>
+      </c>
+      <c r="S166">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>206</v>
+      </c>
+      <c r="B167" t="s">
+        <v>207</v>
+      </c>
+      <c r="C167" t="s">
+        <v>215</v>
+      </c>
+      <c r="D167" t="s">
+        <v>216</v>
+      </c>
+      <c r="E167" t="s">
+        <v>32</v>
+      </c>
+      <c r="F167" t="s">
+        <v>33</v>
+      </c>
+      <c r="G167" t="s">
+        <v>407</v>
+      </c>
+      <c r="H167" t="s">
+        <v>132</v>
+      </c>
+      <c r="I167" t="s">
+        <v>133</v>
+      </c>
+      <c r="J167">
+        <v>78.959999999999994</v>
+      </c>
+      <c r="K167" t="s">
+        <v>40</v>
+      </c>
+      <c r="L167" t="s">
+        <v>403</v>
+      </c>
+      <c r="M167" t="s">
+        <v>18</v>
+      </c>
+      <c r="N167" t="s">
+        <v>19</v>
+      </c>
+      <c r="O167" t="s">
+        <v>20</v>
+      </c>
+      <c r="P167" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>232</v>
+      </c>
+      <c r="R167" t="s">
+        <v>531</v>
+      </c>
+      <c r="S167">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>206</v>
+      </c>
+      <c r="B168" t="s">
+        <v>207</v>
+      </c>
+      <c r="C168" t="s">
+        <v>221</v>
+      </c>
+      <c r="D168" t="s">
+        <v>222</v>
+      </c>
+      <c r="E168" t="s">
+        <v>223</v>
+      </c>
+      <c r="F168" t="s">
+        <v>151</v>
+      </c>
+      <c r="G168" t="s">
+        <v>409</v>
+      </c>
+      <c r="H168" t="s">
+        <v>132</v>
+      </c>
+      <c r="I168" t="s">
+        <v>133</v>
+      </c>
+      <c r="J168">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="K168" t="s">
+        <v>23</v>
+      </c>
+      <c r="L168" t="s">
+        <v>403</v>
+      </c>
+      <c r="M168" t="s">
+        <v>18</v>
+      </c>
+      <c r="N168" t="s">
+        <v>19</v>
+      </c>
+      <c r="O168" t="s">
+        <v>20</v>
+      </c>
+      <c r="P168" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>232</v>
+      </c>
+      <c r="R168" t="s">
+        <v>531</v>
+      </c>
+      <c r="S168">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>206</v>
+      </c>
+      <c r="B169" t="s">
+        <v>207</v>
+      </c>
+      <c r="C169" t="s">
+        <v>208</v>
+      </c>
+      <c r="D169" t="s">
+        <v>209</v>
+      </c>
+      <c r="E169" t="s">
+        <v>210</v>
+      </c>
+      <c r="F169" t="s">
+        <v>118</v>
+      </c>
+      <c r="G169" t="s">
+        <v>402</v>
+      </c>
+      <c r="H169" t="s">
+        <v>132</v>
+      </c>
+      <c r="I169" t="s">
+        <v>133</v>
+      </c>
+      <c r="J169">
+        <v>98.7</v>
+      </c>
+      <c r="K169" t="s">
+        <v>329</v>
+      </c>
+      <c r="L169" t="s">
+        <v>403</v>
+      </c>
+      <c r="M169" t="s">
+        <v>18</v>
+      </c>
+      <c r="N169" t="s">
+        <v>19</v>
+      </c>
+      <c r="O169" t="s">
+        <v>20</v>
+      </c>
+      <c r="P169" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>232</v>
+      </c>
+      <c r="R169" t="s">
+        <v>531</v>
+      </c>
+      <c r="S169">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>206</v>
+      </c>
+      <c r="B170" t="s">
+        <v>207</v>
+      </c>
+      <c r="C170" t="s">
+        <v>212</v>
+      </c>
+      <c r="D170" t="s">
+        <v>213</v>
+      </c>
+      <c r="E170" t="s">
+        <v>214</v>
+      </c>
+      <c r="F170" t="s">
+        <v>70</v>
+      </c>
+      <c r="G170" t="s">
+        <v>402</v>
+      </c>
+      <c r="H170" t="s">
+        <v>425</v>
+      </c>
+      <c r="I170" t="s">
+        <v>426</v>
+      </c>
+      <c r="J170">
+        <v>34.86</v>
+      </c>
+      <c r="K170" t="s">
+        <v>22</v>
+      </c>
+      <c r="L170" t="s">
+        <v>403</v>
+      </c>
+      <c r="M170" t="s">
+        <v>18</v>
+      </c>
+      <c r="N170" t="s">
+        <v>19</v>
+      </c>
+      <c r="O170" t="s">
+        <v>20</v>
+      </c>
+      <c r="P170" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>428</v>
+      </c>
+      <c r="R170" t="s">
+        <v>531</v>
+      </c>
+      <c r="S170">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>206</v>
+      </c>
+      <c r="B171" t="s">
+        <v>207</v>
+      </c>
+      <c r="C171" t="s">
+        <v>233</v>
+      </c>
+      <c r="D171" t="s">
+        <v>222</v>
+      </c>
+      <c r="E171" t="s">
+        <v>234</v>
+      </c>
+      <c r="F171" t="s">
+        <v>110</v>
+      </c>
+      <c r="G171" t="s">
+        <v>429</v>
+      </c>
+      <c r="H171" t="s">
+        <v>425</v>
+      </c>
+      <c r="I171" t="s">
+        <v>426</v>
+      </c>
+      <c r="J171">
+        <v>17.43</v>
+      </c>
+      <c r="K171" t="s">
+        <v>23</v>
+      </c>
+      <c r="L171" t="s">
+        <v>403</v>
+      </c>
+      <c r="M171" t="s">
+        <v>18</v>
+      </c>
+      <c r="N171" t="s">
+        <v>19</v>
+      </c>
+      <c r="O171" t="s">
+        <v>20</v>
+      </c>
+      <c r="P171" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>428</v>
+      </c>
+      <c r="R171" t="s">
+        <v>531</v>
+      </c>
+      <c r="S171">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>206</v>
+      </c>
+      <c r="B172" t="s">
+        <v>207</v>
+      </c>
+      <c r="C172" t="s">
+        <v>233</v>
+      </c>
+      <c r="D172" t="s">
+        <v>222</v>
+      </c>
+      <c r="E172" t="s">
+        <v>234</v>
+      </c>
+      <c r="F172" t="s">
+        <v>110</v>
+      </c>
+      <c r="G172" t="s">
+        <v>430</v>
+      </c>
+      <c r="H172" t="s">
+        <v>425</v>
+      </c>
+      <c r="I172" t="s">
+        <v>426</v>
+      </c>
+      <c r="J172">
+        <v>17.43</v>
+      </c>
+      <c r="K172" t="s">
+        <v>23</v>
+      </c>
+      <c r="L172" t="s">
+        <v>403</v>
+      </c>
+      <c r="M172" t="s">
+        <v>18</v>
+      </c>
+      <c r="N172" t="s">
+        <v>19</v>
+      </c>
+      <c r="O172" t="s">
+        <v>20</v>
+      </c>
+      <c r="P172" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>428</v>
+      </c>
+      <c r="R172" t="s">
+        <v>531</v>
+      </c>
+      <c r="S172">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>206</v>
+      </c>
+      <c r="B173" t="s">
+        <v>207</v>
+      </c>
+      <c r="C173" t="s">
+        <v>251</v>
+      </c>
+      <c r="D173" t="s">
+        <v>252</v>
+      </c>
+      <c r="E173" t="s">
+        <v>198</v>
+      </c>
+      <c r="F173" t="s">
+        <v>119</v>
+      </c>
+      <c r="G173" t="s">
+        <v>431</v>
+      </c>
+      <c r="H173" t="s">
+        <v>98</v>
+      </c>
+      <c r="I173" t="s">
+        <v>99</v>
+      </c>
+      <c r="J173">
+        <v>39.32</v>
+      </c>
+      <c r="K173" t="s">
+        <v>23</v>
+      </c>
+      <c r="L173" t="s">
+        <v>403</v>
+      </c>
+      <c r="M173" t="s">
+        <v>18</v>
+      </c>
+      <c r="N173" t="s">
+        <v>19</v>
+      </c>
+      <c r="O173" t="s">
+        <v>20</v>
+      </c>
+      <c r="P173" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>432</v>
+      </c>
+      <c r="R173" t="s">
+        <v>531</v>
+      </c>
+      <c r="S173">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>206</v>
+      </c>
+      <c r="B174" t="s">
+        <v>207</v>
+      </c>
+      <c r="C174" t="s">
+        <v>212</v>
+      </c>
+      <c r="D174" t="s">
+        <v>213</v>
+      </c>
+      <c r="E174" t="s">
+        <v>214</v>
+      </c>
+      <c r="F174" t="s">
+        <v>70</v>
+      </c>
+      <c r="G174" t="s">
+        <v>402</v>
+      </c>
+      <c r="H174" t="s">
+        <v>98</v>
+      </c>
+      <c r="I174" t="s">
+        <v>99</v>
+      </c>
+      <c r="J174">
+        <v>39.32</v>
+      </c>
+      <c r="K174" t="s">
+        <v>23</v>
+      </c>
+      <c r="L174" t="s">
+        <v>403</v>
+      </c>
+      <c r="M174" t="s">
+        <v>18</v>
+      </c>
+      <c r="N174" t="s">
+        <v>19</v>
+      </c>
+      <c r="O174" t="s">
+        <v>20</v>
+      </c>
+      <c r="P174" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>432</v>
+      </c>
+      <c r="R174" t="s">
+        <v>531</v>
+      </c>
+      <c r="S174">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>206</v>
+      </c>
+      <c r="B175" t="s">
+        <v>207</v>
+      </c>
+      <c r="C175" t="s">
+        <v>233</v>
+      </c>
+      <c r="D175" t="s">
+        <v>222</v>
+      </c>
+      <c r="E175" t="s">
+        <v>234</v>
+      </c>
+      <c r="F175" t="s">
+        <v>110</v>
+      </c>
+      <c r="G175" t="s">
+        <v>429</v>
+      </c>
+      <c r="H175" t="s">
+        <v>98</v>
+      </c>
+      <c r="I175" t="s">
+        <v>99</v>
+      </c>
+      <c r="J175">
+        <v>39.32</v>
+      </c>
+      <c r="K175" t="s">
+        <v>23</v>
+      </c>
+      <c r="L175" t="s">
+        <v>403</v>
+      </c>
+      <c r="M175" t="s">
+        <v>18</v>
+      </c>
+      <c r="N175" t="s">
+        <v>19</v>
+      </c>
+      <c r="O175" t="s">
+        <v>20</v>
+      </c>
+      <c r="P175" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>432</v>
+      </c>
+      <c r="R175" t="s">
+        <v>531</v>
+      </c>
+      <c r="S175">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>206</v>
+      </c>
+      <c r="B176" t="s">
+        <v>207</v>
+      </c>
+      <c r="C176" t="s">
+        <v>251</v>
+      </c>
+      <c r="D176" t="s">
+        <v>252</v>
+      </c>
+      <c r="E176" t="s">
+        <v>198</v>
+      </c>
+      <c r="F176" t="s">
+        <v>119</v>
+      </c>
+      <c r="G176" t="s">
+        <v>402</v>
+      </c>
+      <c r="H176" t="s">
+        <v>433</v>
+      </c>
+      <c r="I176" t="s">
+        <v>434</v>
+      </c>
+      <c r="J176">
+        <v>15.1</v>
+      </c>
+      <c r="K176" t="s">
+        <v>23</v>
+      </c>
+      <c r="L176" t="s">
+        <v>403</v>
+      </c>
+      <c r="M176" t="s">
+        <v>18</v>
+      </c>
+      <c r="N176" t="s">
+        <v>19</v>
+      </c>
+      <c r="O176" t="s">
+        <v>20</v>
+      </c>
+      <c r="P176" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>436</v>
+      </c>
+      <c r="R176" t="s">
+        <v>531</v>
+      </c>
+      <c r="S176">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>206</v>
+      </c>
+      <c r="B177" t="s">
+        <v>207</v>
+      </c>
+      <c r="C177" t="s">
+        <v>215</v>
+      </c>
+      <c r="D177" t="s">
+        <v>216</v>
+      </c>
+      <c r="E177" t="s">
+        <v>32</v>
+      </c>
+      <c r="F177" t="s">
+        <v>33</v>
+      </c>
+      <c r="G177" t="s">
+        <v>407</v>
+      </c>
+      <c r="H177" t="s">
+        <v>319</v>
+      </c>
+      <c r="I177" t="s">
+        <v>320</v>
+      </c>
+      <c r="J177">
+        <v>1.81</v>
+      </c>
+      <c r="K177" t="s">
+        <v>23</v>
+      </c>
+      <c r="L177" t="s">
+        <v>403</v>
+      </c>
+      <c r="M177" t="s">
+        <v>18</v>
+      </c>
+      <c r="N177" t="s">
+        <v>19</v>
+      </c>
+      <c r="O177" t="s">
+        <v>20</v>
+      </c>
+      <c r="P177" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>322</v>
+      </c>
+      <c r="R177" t="s">
+        <v>531</v>
+      </c>
+      <c r="S177">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>206</v>
+      </c>
+      <c r="B178" t="s">
+        <v>207</v>
+      </c>
+      <c r="C178" t="s">
+        <v>233</v>
+      </c>
+      <c r="D178" t="s">
+        <v>222</v>
+      </c>
+      <c r="E178" t="s">
+        <v>234</v>
+      </c>
+      <c r="F178" t="s">
+        <v>110</v>
+      </c>
+      <c r="G178" t="s">
+        <v>429</v>
+      </c>
+      <c r="H178" t="s">
+        <v>437</v>
+      </c>
+      <c r="I178" t="s">
+        <v>438</v>
+      </c>
+      <c r="J178">
+        <v>9.92</v>
+      </c>
+      <c r="K178" t="s">
+        <v>23</v>
+      </c>
+      <c r="L178" t="s">
+        <v>403</v>
+      </c>
+      <c r="M178" t="s">
+        <v>18</v>
+      </c>
+      <c r="N178" t="s">
+        <v>19</v>
+      </c>
+      <c r="O178" t="s">
+        <v>20</v>
+      </c>
+      <c r="P178" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>440</v>
+      </c>
+      <c r="R178" t="s">
+        <v>531</v>
+      </c>
+      <c r="S178">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>206</v>
+      </c>
+      <c r="B179" t="s">
+        <v>207</v>
+      </c>
+      <c r="C179" t="s">
+        <v>208</v>
+      </c>
+      <c r="D179" t="s">
+        <v>209</v>
+      </c>
+      <c r="E179" t="s">
+        <v>210</v>
+      </c>
+      <c r="F179" t="s">
+        <v>118</v>
+      </c>
+      <c r="G179" t="s">
+        <v>424</v>
+      </c>
+      <c r="H179" t="s">
+        <v>441</v>
+      </c>
+      <c r="I179" t="s">
+        <v>442</v>
+      </c>
+      <c r="J179">
+        <v>18.21</v>
+      </c>
+      <c r="K179" t="s">
+        <v>23</v>
+      </c>
+      <c r="L179" t="s">
+        <v>403</v>
+      </c>
+      <c r="M179" t="s">
+        <v>18</v>
+      </c>
+      <c r="N179" t="s">
+        <v>19</v>
+      </c>
+      <c r="O179" t="s">
+        <v>20</v>
+      </c>
+      <c r="P179" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>444</v>
+      </c>
+      <c r="R179" t="s">
+        <v>531</v>
+      </c>
+      <c r="S179">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>206</v>
+      </c>
+      <c r="B180" t="s">
+        <v>207</v>
+      </c>
+      <c r="C180" t="s">
+        <v>208</v>
+      </c>
+      <c r="D180" t="s">
+        <v>209</v>
+      </c>
+      <c r="E180" t="s">
+        <v>210</v>
+      </c>
+      <c r="F180" t="s">
+        <v>118</v>
+      </c>
+      <c r="G180" t="s">
+        <v>424</v>
+      </c>
+      <c r="H180" t="s">
+        <v>445</v>
+      </c>
+      <c r="I180" t="s">
+        <v>446</v>
+      </c>
+      <c r="J180">
+        <v>18.75</v>
+      </c>
+      <c r="K180" t="s">
+        <v>23</v>
+      </c>
+      <c r="L180" t="s">
+        <v>403</v>
+      </c>
+      <c r="M180" t="s">
+        <v>18</v>
+      </c>
+      <c r="N180" t="s">
+        <v>19</v>
+      </c>
+      <c r="O180" t="s">
+        <v>20</v>
+      </c>
+      <c r="P180" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>448</v>
+      </c>
+      <c r="R180" t="s">
+        <v>531</v>
+      </c>
+      <c r="S180">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>206</v>
+      </c>
+      <c r="B181" t="s">
+        <v>207</v>
+      </c>
+      <c r="C181" t="s">
+        <v>233</v>
+      </c>
+      <c r="D181" t="s">
+        <v>222</v>
+      </c>
+      <c r="E181" t="s">
+        <v>234</v>
+      </c>
+      <c r="F181" t="s">
+        <v>110</v>
+      </c>
+      <c r="G181" t="s">
+        <v>429</v>
+      </c>
+      <c r="H181" t="s">
+        <v>449</v>
+      </c>
+      <c r="I181" t="s">
+        <v>450</v>
+      </c>
+      <c r="J181">
+        <v>18.510000000000002</v>
+      </c>
+      <c r="K181" t="s">
+        <v>23</v>
+      </c>
+      <c r="L181" t="s">
+        <v>403</v>
+      </c>
+      <c r="M181" t="s">
+        <v>18</v>
+      </c>
+      <c r="N181" t="s">
+        <v>19</v>
+      </c>
+      <c r="O181" t="s">
+        <v>20</v>
+      </c>
+      <c r="P181" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>275</v>
+      </c>
+      <c r="R181" t="s">
+        <v>531</v>
+      </c>
+      <c r="S181">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>206</v>
+      </c>
+      <c r="B182" t="s">
+        <v>207</v>
+      </c>
+      <c r="C182" t="s">
+        <v>233</v>
+      </c>
+      <c r="D182" t="s">
+        <v>222</v>
+      </c>
+      <c r="E182" t="s">
+        <v>234</v>
+      </c>
+      <c r="F182" t="s">
+        <v>110</v>
+      </c>
+      <c r="G182" t="s">
+        <v>430</v>
+      </c>
+      <c r="H182" t="s">
+        <v>449</v>
+      </c>
+      <c r="I182" t="s">
+        <v>450</v>
+      </c>
+      <c r="J182">
+        <v>18.510000000000002</v>
+      </c>
+      <c r="K182" t="s">
+        <v>23</v>
+      </c>
+      <c r="L182" t="s">
+        <v>403</v>
+      </c>
+      <c r="M182" t="s">
+        <v>18</v>
+      </c>
+      <c r="N182" t="s">
+        <v>19</v>
+      </c>
+      <c r="O182" t="s">
+        <v>20</v>
+      </c>
+      <c r="P182" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>275</v>
+      </c>
+      <c r="R182" t="s">
+        <v>531</v>
+      </c>
+      <c r="S182">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>206</v>
+      </c>
+      <c r="B183" t="s">
+        <v>207</v>
+      </c>
+      <c r="C183" t="s">
+        <v>208</v>
+      </c>
+      <c r="D183" t="s">
+        <v>209</v>
+      </c>
+      <c r="E183" t="s">
+        <v>210</v>
+      </c>
+      <c r="F183" t="s">
+        <v>118</v>
+      </c>
+      <c r="G183" t="s">
+        <v>424</v>
+      </c>
+      <c r="H183" t="s">
+        <v>452</v>
+      </c>
+      <c r="I183" t="s">
+        <v>453</v>
+      </c>
+      <c r="J183">
+        <v>18.21</v>
+      </c>
+      <c r="K183" t="s">
+        <v>23</v>
+      </c>
+      <c r="L183" t="s">
+        <v>403</v>
+      </c>
+      <c r="M183" t="s">
+        <v>18</v>
+      </c>
+      <c r="N183" t="s">
+        <v>19</v>
+      </c>
+      <c r="O183" t="s">
+        <v>20</v>
+      </c>
+      <c r="P183" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>444</v>
+      </c>
+      <c r="R183" t="s">
+        <v>531</v>
+      </c>
+      <c r="S183">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>206</v>
+      </c>
+      <c r="B184" t="s">
+        <v>207</v>
+      </c>
+      <c r="C184" t="s">
+        <v>215</v>
+      </c>
+      <c r="D184" t="s">
+        <v>216</v>
+      </c>
+      <c r="E184" t="s">
+        <v>32</v>
+      </c>
+      <c r="F184" t="s">
+        <v>33</v>
+      </c>
+      <c r="G184" t="s">
+        <v>407</v>
+      </c>
+      <c r="H184" t="s">
+        <v>24</v>
+      </c>
+      <c r="I184" t="s">
+        <v>25</v>
+      </c>
+      <c r="J184">
+        <v>6.19</v>
+      </c>
+      <c r="K184" t="s">
+        <v>23</v>
+      </c>
+      <c r="L184" t="s">
+        <v>403</v>
+      </c>
+      <c r="M184" t="s">
+        <v>18</v>
+      </c>
+      <c r="N184" t="s">
+        <v>19</v>
+      </c>
+      <c r="O184" t="s">
+        <v>20</v>
+      </c>
+      <c r="P184" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>455</v>
+      </c>
+      <c r="R184" t="s">
+        <v>531</v>
+      </c>
+      <c r="S184">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>206</v>
+      </c>
+      <c r="B185" t="s">
+        <v>207</v>
+      </c>
+      <c r="C185" t="s">
+        <v>208</v>
+      </c>
+      <c r="D185" t="s">
+        <v>209</v>
+      </c>
+      <c r="E185" t="s">
+        <v>210</v>
+      </c>
+      <c r="F185" t="s">
+        <v>118</v>
+      </c>
+      <c r="G185" t="s">
+        <v>424</v>
+      </c>
+      <c r="H185" t="s">
+        <v>456</v>
+      </c>
+      <c r="I185" t="s">
+        <v>457</v>
+      </c>
+      <c r="J185">
+        <v>18.53</v>
+      </c>
+      <c r="K185" t="s">
+        <v>23</v>
+      </c>
+      <c r="L185" t="s">
+        <v>403</v>
+      </c>
+      <c r="M185" t="s">
+        <v>18</v>
+      </c>
+      <c r="N185" t="s">
+        <v>19</v>
+      </c>
+      <c r="O185" t="s">
+        <v>20</v>
+      </c>
+      <c r="P185" t="s">
+        <v>458</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>459</v>
+      </c>
+      <c r="R185" t="s">
+        <v>531</v>
+      </c>
+      <c r="S185">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>206</v>
+      </c>
+      <c r="B186" t="s">
+        <v>207</v>
+      </c>
+      <c r="C186" t="s">
+        <v>208</v>
+      </c>
+      <c r="D186" t="s">
+        <v>209</v>
+      </c>
+      <c r="E186" t="s">
+        <v>210</v>
+      </c>
+      <c r="F186" t="s">
+        <v>118</v>
+      </c>
+      <c r="G186" t="s">
+        <v>424</v>
+      </c>
+      <c r="H186" t="s">
+        <v>460</v>
+      </c>
+      <c r="I186" t="s">
+        <v>461</v>
+      </c>
+      <c r="J186">
+        <v>18.75</v>
+      </c>
+      <c r="K186" t="s">
+        <v>23</v>
+      </c>
+      <c r="L186" t="s">
+        <v>403</v>
+      </c>
+      <c r="M186" t="s">
+        <v>18</v>
+      </c>
+      <c r="N186" t="s">
+        <v>19</v>
+      </c>
+      <c r="O186" t="s">
+        <v>20</v>
+      </c>
+      <c r="P186" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>448</v>
+      </c>
+      <c r="R186" t="s">
+        <v>531</v>
+      </c>
+      <c r="S186">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>206</v>
+      </c>
+      <c r="B187" t="s">
+        <v>207</v>
+      </c>
+      <c r="C187" t="s">
+        <v>215</v>
+      </c>
+      <c r="D187" t="s">
+        <v>216</v>
+      </c>
+      <c r="E187" t="s">
+        <v>32</v>
+      </c>
+      <c r="F187" t="s">
+        <v>33</v>
+      </c>
+      <c r="G187" t="s">
+        <v>463</v>
+      </c>
+      <c r="H187" t="s">
+        <v>148</v>
+      </c>
+      <c r="I187" t="s">
+        <v>149</v>
+      </c>
+      <c r="J187">
+        <v>51.16</v>
+      </c>
+      <c r="K187" t="s">
+        <v>40</v>
+      </c>
+      <c r="L187" t="s">
+        <v>403</v>
+      </c>
+      <c r="M187" t="s">
+        <v>18</v>
+      </c>
+      <c r="N187" t="s">
+        <v>19</v>
+      </c>
+      <c r="O187" t="s">
+        <v>20</v>
+      </c>
+      <c r="P187" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>464</v>
+      </c>
+      <c r="R187" t="s">
+        <v>531</v>
+      </c>
+      <c r="S187">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>206</v>
+      </c>
+      <c r="B188" t="s">
+        <v>207</v>
+      </c>
+      <c r="C188" t="s">
+        <v>208</v>
+      </c>
+      <c r="D188" t="s">
+        <v>209</v>
+      </c>
+      <c r="E188" t="s">
+        <v>210</v>
+      </c>
+      <c r="F188" t="s">
+        <v>118</v>
+      </c>
+      <c r="G188" t="s">
+        <v>465</v>
+      </c>
+      <c r="H188" t="s">
+        <v>148</v>
+      </c>
+      <c r="I188" t="s">
+        <v>149</v>
+      </c>
+      <c r="J188">
+        <v>12.79</v>
+      </c>
+      <c r="K188" t="s">
+        <v>23</v>
+      </c>
+      <c r="L188" t="s">
+        <v>403</v>
+      </c>
+      <c r="M188" t="s">
+        <v>18</v>
+      </c>
+      <c r="N188" t="s">
+        <v>19</v>
+      </c>
+      <c r="O188" t="s">
+        <v>20</v>
+      </c>
+      <c r="P188" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>464</v>
+      </c>
+      <c r="R188" t="s">
+        <v>531</v>
+      </c>
+      <c r="S188">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>206</v>
+      </c>
+      <c r="B189" t="s">
+        <v>207</v>
+      </c>
+      <c r="C189" t="s">
+        <v>466</v>
+      </c>
+      <c r="D189" t="s">
+        <v>222</v>
+      </c>
+      <c r="E189" t="s">
+        <v>467</v>
+      </c>
+      <c r="F189" t="s">
+        <v>110</v>
+      </c>
+      <c r="G189" t="s">
+        <v>468</v>
+      </c>
+      <c r="H189" t="s">
+        <v>148</v>
+      </c>
+      <c r="I189" t="s">
+        <v>149</v>
+      </c>
+      <c r="J189">
+        <v>12.79</v>
+      </c>
+      <c r="K189" t="s">
+        <v>23</v>
+      </c>
+      <c r="L189" t="s">
+        <v>403</v>
+      </c>
+      <c r="M189" t="s">
+        <v>18</v>
+      </c>
+      <c r="N189" t="s">
+        <v>19</v>
+      </c>
+      <c r="O189" t="s">
+        <v>20</v>
+      </c>
+      <c r="P189" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>464</v>
+      </c>
+      <c r="R189" t="s">
+        <v>531</v>
+      </c>
+      <c r="S189">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>206</v>
+      </c>
+      <c r="B190" t="s">
+        <v>207</v>
+      </c>
+      <c r="C190" t="s">
+        <v>215</v>
+      </c>
+      <c r="D190" t="s">
+        <v>216</v>
+      </c>
+      <c r="E190" t="s">
+        <v>32</v>
+      </c>
+      <c r="F190" t="s">
+        <v>33</v>
+      </c>
+      <c r="G190" t="s">
+        <v>407</v>
+      </c>
+      <c r="H190" t="s">
+        <v>57</v>
+      </c>
+      <c r="I190" t="s">
+        <v>58</v>
+      </c>
+      <c r="J190">
+        <v>30.65</v>
+      </c>
+      <c r="K190" t="s">
+        <v>23</v>
+      </c>
+      <c r="L190" t="s">
+        <v>403</v>
+      </c>
+      <c r="M190" t="s">
+        <v>18</v>
+      </c>
+      <c r="N190" t="s">
+        <v>19</v>
+      </c>
+      <c r="O190" t="s">
+        <v>20</v>
+      </c>
+      <c r="P190" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>469</v>
+      </c>
+      <c r="R190" t="s">
+        <v>531</v>
+      </c>
+      <c r="S190">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>206</v>
+      </c>
+      <c r="B191" t="s">
+        <v>207</v>
+      </c>
+      <c r="C191" t="s">
+        <v>221</v>
+      </c>
+      <c r="D191" t="s">
+        <v>222</v>
+      </c>
+      <c r="E191" t="s">
+        <v>223</v>
+      </c>
+      <c r="F191" t="s">
+        <v>151</v>
+      </c>
+      <c r="G191" t="s">
+        <v>409</v>
+      </c>
+      <c r="H191" t="s">
+        <v>57</v>
+      </c>
+      <c r="I191" t="s">
+        <v>58</v>
+      </c>
+      <c r="J191">
+        <v>30.65</v>
+      </c>
+      <c r="K191" t="s">
+        <v>23</v>
+      </c>
+      <c r="L191" t="s">
+        <v>403</v>
+      </c>
+      <c r="M191" t="s">
+        <v>18</v>
+      </c>
+      <c r="N191" t="s">
+        <v>19</v>
+      </c>
+      <c r="O191" t="s">
+        <v>20</v>
+      </c>
+      <c r="P191" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>469</v>
+      </c>
+      <c r="R191" t="s">
+        <v>531</v>
+      </c>
+      <c r="S191">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>206</v>
+      </c>
+      <c r="B192" t="s">
+        <v>207</v>
+      </c>
+      <c r="C192" t="s">
+        <v>251</v>
+      </c>
+      <c r="D192" t="s">
+        <v>252</v>
+      </c>
+      <c r="E192" t="s">
+        <v>198</v>
+      </c>
+      <c r="F192" t="s">
+        <v>119</v>
+      </c>
+      <c r="G192" t="s">
+        <v>405</v>
+      </c>
+      <c r="H192" t="s">
+        <v>57</v>
+      </c>
+      <c r="I192" t="s">
+        <v>58</v>
+      </c>
+      <c r="J192">
+        <v>30.65</v>
+      </c>
+      <c r="K192" t="s">
+        <v>23</v>
+      </c>
+      <c r="L192" t="s">
+        <v>403</v>
+      </c>
+      <c r="M192" t="s">
+        <v>18</v>
+      </c>
+      <c r="N192" t="s">
+        <v>19</v>
+      </c>
+      <c r="O192" t="s">
+        <v>20</v>
+      </c>
+      <c r="P192" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>469</v>
+      </c>
+      <c r="R192" t="s">
+        <v>531</v>
+      </c>
+      <c r="S192">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>206</v>
+      </c>
+      <c r="B193" t="s">
+        <v>207</v>
+      </c>
+      <c r="C193" t="s">
+        <v>233</v>
+      </c>
+      <c r="D193" t="s">
+        <v>222</v>
+      </c>
+      <c r="E193" t="s">
+        <v>234</v>
+      </c>
+      <c r="F193" t="s">
+        <v>110</v>
+      </c>
+      <c r="G193" t="s">
+        <v>429</v>
+      </c>
+      <c r="H193" t="s">
+        <v>57</v>
+      </c>
+      <c r="I193" t="s">
+        <v>58</v>
+      </c>
+      <c r="J193">
+        <v>30.65</v>
+      </c>
+      <c r="K193" t="s">
+        <v>23</v>
+      </c>
+      <c r="L193" t="s">
+        <v>403</v>
+      </c>
+      <c r="M193" t="s">
+        <v>18</v>
+      </c>
+      <c r="N193" t="s">
+        <v>19</v>
+      </c>
+      <c r="O193" t="s">
+        <v>20</v>
+      </c>
+      <c r="P193" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>469</v>
+      </c>
+      <c r="R193" t="s">
+        <v>531</v>
+      </c>
+      <c r="S193">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>206</v>
+      </c>
+      <c r="B194" t="s">
+        <v>207</v>
+      </c>
+      <c r="C194" t="s">
+        <v>221</v>
+      </c>
+      <c r="D194" t="s">
+        <v>222</v>
+      </c>
+      <c r="E194" t="s">
+        <v>223</v>
+      </c>
+      <c r="F194" t="s">
+        <v>151</v>
+      </c>
+      <c r="G194" t="s">
+        <v>409</v>
+      </c>
+      <c r="H194" t="s">
+        <v>73</v>
+      </c>
+      <c r="I194" t="s">
+        <v>74</v>
+      </c>
+      <c r="J194">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="K194" t="s">
+        <v>23</v>
+      </c>
+      <c r="L194" t="s">
+        <v>403</v>
+      </c>
+      <c r="M194" t="s">
+        <v>18</v>
+      </c>
+      <c r="N194" t="s">
+        <v>19</v>
+      </c>
+      <c r="O194" t="s">
+        <v>20</v>
+      </c>
+      <c r="P194" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>470</v>
+      </c>
+      <c r="R194" t="s">
+        <v>531</v>
+      </c>
+      <c r="S194">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>206</v>
+      </c>
+      <c r="B195" t="s">
+        <v>207</v>
+      </c>
+      <c r="C195" t="s">
+        <v>208</v>
+      </c>
+      <c r="D195" t="s">
+        <v>209</v>
+      </c>
+      <c r="E195" t="s">
+        <v>210</v>
+      </c>
+      <c r="F195" t="s">
+        <v>118</v>
+      </c>
+      <c r="G195" t="s">
+        <v>405</v>
+      </c>
+      <c r="H195" t="s">
+        <v>73</v>
+      </c>
+      <c r="I195" t="s">
+        <v>74</v>
+      </c>
+      <c r="J195">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="K195" t="s">
+        <v>23</v>
+      </c>
+      <c r="L195" t="s">
+        <v>403</v>
+      </c>
+      <c r="M195" t="s">
+        <v>18</v>
+      </c>
+      <c r="N195" t="s">
+        <v>19</v>
+      </c>
+      <c r="O195" t="s">
+        <v>20</v>
+      </c>
+      <c r="P195" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>470</v>
+      </c>
+      <c r="R195" t="s">
+        <v>531</v>
+      </c>
+      <c r="S195">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>206</v>
+      </c>
+      <c r="B196" t="s">
+        <v>207</v>
+      </c>
+      <c r="C196" t="s">
+        <v>212</v>
+      </c>
+      <c r="D196" t="s">
+        <v>213</v>
+      </c>
+      <c r="E196" t="s">
+        <v>214</v>
+      </c>
+      <c r="F196" t="s">
+        <v>70</v>
+      </c>
+      <c r="G196" t="s">
+        <v>402</v>
+      </c>
+      <c r="H196" t="s">
+        <v>73</v>
+      </c>
+      <c r="I196" t="s">
+        <v>74</v>
+      </c>
+      <c r="J196">
+        <v>101.1</v>
+      </c>
+      <c r="K196" t="s">
+        <v>471</v>
+      </c>
+      <c r="L196" t="s">
+        <v>403</v>
+      </c>
+      <c r="M196" t="s">
+        <v>18</v>
+      </c>
+      <c r="N196" t="s">
+        <v>19</v>
+      </c>
+      <c r="O196" t="s">
+        <v>20</v>
+      </c>
+      <c r="P196" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>470</v>
+      </c>
+      <c r="R196" t="s">
+        <v>531</v>
+      </c>
+      <c r="S196">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>206</v>
+      </c>
+      <c r="B197" t="s">
+        <v>207</v>
+      </c>
+      <c r="C197" t="s">
+        <v>233</v>
+      </c>
+      <c r="D197" t="s">
+        <v>222</v>
+      </c>
+      <c r="E197" t="s">
+        <v>234</v>
+      </c>
+      <c r="F197" t="s">
+        <v>110</v>
+      </c>
+      <c r="G197" t="s">
+        <v>429</v>
+      </c>
+      <c r="H197" t="s">
+        <v>73</v>
+      </c>
+      <c r="I197" t="s">
+        <v>74</v>
+      </c>
+      <c r="J197">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="K197" t="s">
+        <v>23</v>
+      </c>
+      <c r="L197" t="s">
+        <v>403</v>
+      </c>
+      <c r="M197" t="s">
+        <v>18</v>
+      </c>
+      <c r="N197" t="s">
+        <v>19</v>
+      </c>
+      <c r="O197" t="s">
+        <v>20</v>
+      </c>
+      <c r="P197" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>470</v>
+      </c>
+      <c r="R197" t="s">
+        <v>531</v>
+      </c>
+      <c r="S197">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>206</v>
+      </c>
+      <c r="B198" t="s">
+        <v>207</v>
+      </c>
+      <c r="C198" t="s">
+        <v>233</v>
+      </c>
+      <c r="D198" t="s">
+        <v>222</v>
+      </c>
+      <c r="E198" t="s">
+        <v>234</v>
+      </c>
+      <c r="F198" t="s">
+        <v>110</v>
+      </c>
+      <c r="G198" t="s">
+        <v>472</v>
+      </c>
+      <c r="H198" t="s">
+        <v>73</v>
+      </c>
+      <c r="I198" t="s">
+        <v>74</v>
+      </c>
+      <c r="J198">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="K198" t="s">
+        <v>22</v>
+      </c>
+      <c r="L198" t="s">
+        <v>403</v>
+      </c>
+      <c r="M198" t="s">
+        <v>18</v>
+      </c>
+      <c r="N198" t="s">
+        <v>19</v>
+      </c>
+      <c r="O198" t="s">
+        <v>20</v>
+      </c>
+      <c r="P198" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>470</v>
+      </c>
+      <c r="R198" t="s">
+        <v>531</v>
+      </c>
+      <c r="S198">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>206</v>
+      </c>
+      <c r="B199" t="s">
+        <v>207</v>
+      </c>
+      <c r="C199" t="s">
+        <v>215</v>
+      </c>
+      <c r="D199" t="s">
+        <v>216</v>
+      </c>
+      <c r="E199" t="s">
+        <v>32</v>
+      </c>
+      <c r="F199" t="s">
+        <v>33</v>
+      </c>
+      <c r="G199" t="s">
+        <v>407</v>
+      </c>
+      <c r="H199" t="s">
+        <v>473</v>
+      </c>
+      <c r="I199" t="s">
+        <v>474</v>
+      </c>
+      <c r="J199">
+        <v>13.15</v>
+      </c>
+      <c r="K199" t="s">
+        <v>23</v>
+      </c>
+      <c r="L199" t="s">
+        <v>403</v>
+      </c>
+      <c r="M199" t="s">
+        <v>18</v>
+      </c>
+      <c r="N199" t="s">
+        <v>19</v>
+      </c>
+      <c r="O199" t="s">
+        <v>20</v>
+      </c>
+      <c r="P199" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>476</v>
+      </c>
+      <c r="R199" t="s">
+        <v>531</v>
+      </c>
+      <c r="S199">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>206</v>
+      </c>
+      <c r="B200" t="s">
+        <v>207</v>
+      </c>
+      <c r="C200" t="s">
+        <v>215</v>
+      </c>
+      <c r="D200" t="s">
+        <v>216</v>
+      </c>
+      <c r="E200" t="s">
+        <v>32</v>
+      </c>
+      <c r="F200" t="s">
+        <v>33</v>
+      </c>
+      <c r="G200" t="s">
+        <v>407</v>
+      </c>
+      <c r="H200" t="s">
+        <v>85</v>
+      </c>
+      <c r="I200" t="s">
+        <v>86</v>
+      </c>
+      <c r="J200">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="K200" t="s">
+        <v>22</v>
+      </c>
+      <c r="L200" t="s">
+        <v>403</v>
+      </c>
+      <c r="M200" t="s">
+        <v>18</v>
+      </c>
+      <c r="N200" t="s">
+        <v>19</v>
+      </c>
+      <c r="O200" t="s">
+        <v>20</v>
+      </c>
+      <c r="P200" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>477</v>
+      </c>
+      <c r="R200" t="s">
+        <v>531</v>
+      </c>
+      <c r="S200">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>206</v>
+      </c>
+      <c r="B201" t="s">
+        <v>207</v>
+      </c>
+      <c r="C201" t="s">
+        <v>208</v>
+      </c>
+      <c r="D201" t="s">
+        <v>209</v>
+      </c>
+      <c r="E201" t="s">
+        <v>210</v>
+      </c>
+      <c r="F201" t="s">
+        <v>118</v>
+      </c>
+      <c r="G201" t="s">
+        <v>419</v>
+      </c>
+      <c r="H201" t="s">
+        <v>85</v>
+      </c>
+      <c r="I201" t="s">
+        <v>86</v>
+      </c>
+      <c r="J201">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="K201" t="s">
+        <v>23</v>
+      </c>
+      <c r="L201" t="s">
+        <v>403</v>
+      </c>
+      <c r="M201" t="s">
+        <v>18</v>
+      </c>
+      <c r="N201" t="s">
+        <v>19</v>
+      </c>
+      <c r="O201" t="s">
+        <v>20</v>
+      </c>
+      <c r="P201" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>477</v>
+      </c>
+      <c r="R201" t="s">
+        <v>531</v>
+      </c>
+      <c r="S201">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>206</v>
+      </c>
+      <c r="B202" t="s">
+        <v>207</v>
+      </c>
+      <c r="C202" t="s">
+        <v>233</v>
+      </c>
+      <c r="D202" t="s">
+        <v>222</v>
+      </c>
+      <c r="E202" t="s">
+        <v>234</v>
+      </c>
+      <c r="F202" t="s">
+        <v>110</v>
+      </c>
+      <c r="G202" t="s">
+        <v>429</v>
+      </c>
+      <c r="H202" t="s">
+        <v>85</v>
+      </c>
+      <c r="I202" t="s">
+        <v>86</v>
+      </c>
+      <c r="J202">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="K202" t="s">
+        <v>22</v>
+      </c>
+      <c r="L202" t="s">
+        <v>403</v>
+      </c>
+      <c r="M202" t="s">
+        <v>18</v>
+      </c>
+      <c r="N202" t="s">
+        <v>19</v>
+      </c>
+      <c r="O202" t="s">
+        <v>20</v>
+      </c>
+      <c r="P202" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>477</v>
+      </c>
+      <c r="R202" t="s">
+        <v>531</v>
+      </c>
+      <c r="S202">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>206</v>
+      </c>
+      <c r="B203" t="s">
+        <v>207</v>
+      </c>
+      <c r="C203" t="s">
+        <v>215</v>
+      </c>
+      <c r="D203" t="s">
+        <v>216</v>
+      </c>
+      <c r="E203" t="s">
+        <v>32</v>
+      </c>
+      <c r="F203" t="s">
+        <v>33</v>
+      </c>
+      <c r="G203" t="s">
+        <v>407</v>
+      </c>
+      <c r="H203" t="s">
+        <v>101</v>
+      </c>
+      <c r="I203" t="s">
+        <v>102</v>
+      </c>
+      <c r="J203">
+        <v>58.11</v>
+      </c>
+      <c r="K203" t="s">
+        <v>50</v>
+      </c>
+      <c r="L203" t="s">
+        <v>403</v>
+      </c>
+      <c r="M203" t="s">
+        <v>18</v>
+      </c>
+      <c r="N203" t="s">
+        <v>19</v>
+      </c>
+      <c r="O203" t="s">
+        <v>20</v>
+      </c>
+      <c r="P203" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>478</v>
+      </c>
+      <c r="R203" t="s">
+        <v>531</v>
+      </c>
+      <c r="S203">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>206</v>
+      </c>
+      <c r="B204" t="s">
+        <v>207</v>
+      </c>
+      <c r="C204" t="s">
+        <v>233</v>
+      </c>
+      <c r="D204" t="s">
+        <v>222</v>
+      </c>
+      <c r="E204" t="s">
+        <v>234</v>
+      </c>
+      <c r="F204" t="s">
+        <v>110</v>
+      </c>
+      <c r="G204" t="s">
+        <v>429</v>
+      </c>
+      <c r="H204" t="s">
+        <v>101</v>
+      </c>
+      <c r="I204" t="s">
+        <v>102</v>
+      </c>
+      <c r="J204">
+        <v>38.74</v>
+      </c>
+      <c r="K204" t="s">
+        <v>22</v>
+      </c>
+      <c r="L204" t="s">
+        <v>403</v>
+      </c>
+      <c r="M204" t="s">
+        <v>18</v>
+      </c>
+      <c r="N204" t="s">
+        <v>19</v>
+      </c>
+      <c r="O204" t="s">
+        <v>20</v>
+      </c>
+      <c r="P204" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>478</v>
+      </c>
+      <c r="R204" t="s">
+        <v>531</v>
+      </c>
+      <c r="S204">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>206</v>
+      </c>
+      <c r="B205" t="s">
+        <v>207</v>
+      </c>
+      <c r="C205" t="s">
+        <v>212</v>
+      </c>
+      <c r="D205" t="s">
+        <v>213</v>
+      </c>
+      <c r="E205" t="s">
+        <v>214</v>
+      </c>
+      <c r="F205" t="s">
+        <v>70</v>
+      </c>
+      <c r="G205" t="s">
+        <v>402</v>
+      </c>
+      <c r="H205" t="s">
+        <v>145</v>
+      </c>
+      <c r="I205" t="s">
+        <v>146</v>
+      </c>
+      <c r="J205">
+        <v>21.22</v>
+      </c>
+      <c r="K205" t="s">
+        <v>23</v>
+      </c>
+      <c r="L205" t="s">
+        <v>403</v>
+      </c>
+      <c r="M205" t="s">
+        <v>18</v>
+      </c>
+      <c r="N205" t="s">
+        <v>19</v>
+      </c>
+      <c r="O205" t="s">
+        <v>20</v>
+      </c>
+      <c r="P205" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>479</v>
+      </c>
+      <c r="R205" t="s">
+        <v>531</v>
+      </c>
+      <c r="S205">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>206</v>
+      </c>
+      <c r="B206" t="s">
+        <v>207</v>
+      </c>
+      <c r="C206" t="s">
+        <v>215</v>
+      </c>
+      <c r="D206" t="s">
+        <v>216</v>
+      </c>
+      <c r="E206" t="s">
+        <v>32</v>
+      </c>
+      <c r="F206" t="s">
+        <v>33</v>
+      </c>
+      <c r="G206" t="s">
+        <v>407</v>
+      </c>
+      <c r="H206" t="s">
+        <v>104</v>
+      </c>
+      <c r="I206" t="s">
+        <v>105</v>
+      </c>
+      <c r="J206">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="K206" t="s">
+        <v>23</v>
+      </c>
+      <c r="L206" t="s">
+        <v>403</v>
+      </c>
+      <c r="M206" t="s">
+        <v>18</v>
+      </c>
+      <c r="N206" t="s">
+        <v>19</v>
+      </c>
+      <c r="O206" t="s">
+        <v>20</v>
+      </c>
+      <c r="P206" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>480</v>
+      </c>
+      <c r="R206" t="s">
+        <v>531</v>
+      </c>
+      <c r="S206">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>207</v>
+      </c>
+      <c r="C207" t="s">
+        <v>233</v>
+      </c>
+      <c r="D207" t="s">
+        <v>222</v>
+      </c>
+      <c r="E207" t="s">
+        <v>234</v>
+      </c>
+      <c r="F207" t="s">
+        <v>110</v>
+      </c>
+      <c r="G207" t="s">
+        <v>429</v>
+      </c>
+      <c r="H207" t="s">
+        <v>104</v>
+      </c>
+      <c r="I207" t="s">
+        <v>105</v>
+      </c>
+      <c r="J207">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="K207" t="s">
+        <v>23</v>
+      </c>
+      <c r="L207" t="s">
+        <v>403</v>
+      </c>
+      <c r="M207" t="s">
+        <v>18</v>
+      </c>
+      <c r="N207" t="s">
+        <v>19</v>
+      </c>
+      <c r="O207" t="s">
+        <v>20</v>
+      </c>
+      <c r="P207" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>480</v>
+      </c>
+      <c r="R207" t="s">
+        <v>531</v>
+      </c>
+      <c r="S207">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>206</v>
+      </c>
+      <c r="B208" t="s">
+        <v>207</v>
+      </c>
+      <c r="C208" t="s">
+        <v>215</v>
+      </c>
+      <c r="D208" t="s">
+        <v>216</v>
+      </c>
+      <c r="E208" t="s">
+        <v>32</v>
+      </c>
+      <c r="F208" t="s">
+        <v>33</v>
+      </c>
+      <c r="G208" t="s">
+        <v>407</v>
+      </c>
+      <c r="H208" t="s">
+        <v>38</v>
+      </c>
+      <c r="I208" t="s">
+        <v>39</v>
+      </c>
+      <c r="J208">
+        <v>19.25</v>
+      </c>
+      <c r="K208" t="s">
+        <v>23</v>
+      </c>
+      <c r="L208" t="s">
+        <v>403</v>
+      </c>
+      <c r="M208" t="s">
+        <v>18</v>
+      </c>
+      <c r="N208" t="s">
+        <v>19</v>
+      </c>
+      <c r="O208" t="s">
+        <v>20</v>
+      </c>
+      <c r="P208" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>481</v>
+      </c>
+      <c r="R208" t="s">
+        <v>531</v>
+      </c>
+      <c r="S208">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>206</v>
+      </c>
+      <c r="B209" t="s">
+        <v>207</v>
+      </c>
+      <c r="C209" t="s">
+        <v>212</v>
+      </c>
+      <c r="D209" t="s">
+        <v>213</v>
+      </c>
+      <c r="E209" t="s">
+        <v>214</v>
+      </c>
+      <c r="F209" t="s">
+        <v>70</v>
+      </c>
+      <c r="G209" t="s">
+        <v>402</v>
+      </c>
+      <c r="H209" t="s">
+        <v>38</v>
+      </c>
+      <c r="I209" t="s">
+        <v>39</v>
+      </c>
+      <c r="J209">
+        <v>77</v>
+      </c>
+      <c r="K209" t="s">
+        <v>40</v>
+      </c>
+      <c r="L209" t="s">
+        <v>403</v>
+      </c>
+      <c r="M209" t="s">
+        <v>18</v>
+      </c>
+      <c r="N209" t="s">
+        <v>19</v>
+      </c>
+      <c r="O209" t="s">
+        <v>20</v>
+      </c>
+      <c r="P209" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>481</v>
+      </c>
+      <c r="R209" t="s">
+        <v>531</v>
+      </c>
+      <c r="S209">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>206</v>
+      </c>
+      <c r="B210" t="s">
+        <v>207</v>
+      </c>
+      <c r="C210" t="s">
+        <v>233</v>
+      </c>
+      <c r="D210" t="s">
+        <v>222</v>
+      </c>
+      <c r="E210" t="s">
+        <v>234</v>
+      </c>
+      <c r="F210" t="s">
+        <v>110</v>
+      </c>
+      <c r="G210" t="s">
+        <v>429</v>
+      </c>
+      <c r="H210" t="s">
+        <v>38</v>
+      </c>
+      <c r="I210" t="s">
+        <v>39</v>
+      </c>
+      <c r="J210">
+        <v>38.5</v>
+      </c>
+      <c r="K210" t="s">
+        <v>22</v>
+      </c>
+      <c r="L210" t="s">
+        <v>403</v>
+      </c>
+      <c r="M210" t="s">
+        <v>18</v>
+      </c>
+      <c r="N210" t="s">
+        <v>19</v>
+      </c>
+      <c r="O210" t="s">
+        <v>20</v>
+      </c>
+      <c r="P210" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>481</v>
+      </c>
+      <c r="R210" t="s">
+        <v>531</v>
+      </c>
+      <c r="S210">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>206</v>
+      </c>
+      <c r="B211" t="s">
+        <v>207</v>
+      </c>
+      <c r="C211" t="s">
+        <v>212</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+      <c r="F211" t="s">
+        <v>70</v>
+      </c>
+      <c r="G211" t="s">
+        <v>402</v>
+      </c>
+      <c r="H211" t="s">
+        <v>262</v>
+      </c>
+      <c r="I211" t="s">
+        <v>263</v>
+      </c>
+      <c r="J211">
+        <v>21.56</v>
+      </c>
+      <c r="K211" t="s">
+        <v>40</v>
+      </c>
+      <c r="L211" t="s">
+        <v>403</v>
+      </c>
+      <c r="M211" t="s">
+        <v>18</v>
+      </c>
+      <c r="N211" t="s">
+        <v>19</v>
+      </c>
+      <c r="O211" t="s">
+        <v>20</v>
+      </c>
+      <c r="P211" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>482</v>
+      </c>
+      <c r="R211" t="s">
+        <v>531</v>
+      </c>
+      <c r="S211">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>206</v>
+      </c>
+      <c r="B212" t="s">
+        <v>207</v>
+      </c>
+      <c r="C212" t="s">
+        <v>215</v>
+      </c>
+      <c r="D212" t="s">
+        <v>216</v>
+      </c>
+      <c r="E212" t="s">
+        <v>32</v>
+      </c>
+      <c r="F212" t="s">
+        <v>33</v>
+      </c>
+      <c r="G212" t="s">
+        <v>405</v>
+      </c>
+      <c r="H212" t="s">
+        <v>483</v>
+      </c>
+      <c r="I212" t="s">
+        <v>484</v>
+      </c>
+      <c r="J212">
+        <v>20.14</v>
+      </c>
+      <c r="K212" t="s">
+        <v>23</v>
+      </c>
+      <c r="L212" t="s">
+        <v>403</v>
+      </c>
+      <c r="M212" t="s">
+        <v>18</v>
+      </c>
+      <c r="N212" t="s">
+        <v>19</v>
+      </c>
+      <c r="O212" t="s">
+        <v>20</v>
+      </c>
+      <c r="P212" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>486</v>
+      </c>
+      <c r="R212" t="s">
+        <v>531</v>
+      </c>
+      <c r="S212">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>206</v>
+      </c>
+      <c r="B213" t="s">
+        <v>207</v>
+      </c>
+      <c r="C213" t="s">
+        <v>215</v>
+      </c>
+      <c r="D213" t="s">
+        <v>216</v>
+      </c>
+      <c r="E213" t="s">
+        <v>32</v>
+      </c>
+      <c r="F213" t="s">
+        <v>33</v>
+      </c>
+      <c r="G213" t="s">
+        <v>407</v>
+      </c>
+      <c r="H213" t="s">
+        <v>483</v>
+      </c>
+      <c r="I213" t="s">
+        <v>484</v>
+      </c>
+      <c r="J213">
+        <v>20.14</v>
+      </c>
+      <c r="K213" t="s">
+        <v>23</v>
+      </c>
+      <c r="L213" t="s">
+        <v>403</v>
+      </c>
+      <c r="M213" t="s">
+        <v>18</v>
+      </c>
+      <c r="N213" t="s">
+        <v>19</v>
+      </c>
+      <c r="O213" t="s">
+        <v>20</v>
+      </c>
+      <c r="P213" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>486</v>
+      </c>
+      <c r="R213" t="s">
+        <v>531</v>
+      </c>
+      <c r="S213">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>206</v>
+      </c>
+      <c r="B214" t="s">
+        <v>207</v>
+      </c>
+      <c r="C214" t="s">
+        <v>212</v>
+      </c>
+      <c r="D214" t="s">
+        <v>213</v>
+      </c>
+      <c r="E214" t="s">
+        <v>214</v>
+      </c>
+      <c r="F214" t="s">
+        <v>70</v>
+      </c>
+      <c r="G214" t="s">
+        <v>402</v>
+      </c>
+      <c r="H214" t="s">
+        <v>354</v>
+      </c>
+      <c r="I214" t="s">
+        <v>355</v>
+      </c>
+      <c r="J214">
+        <v>55.2</v>
+      </c>
+      <c r="K214" t="s">
+        <v>23</v>
+      </c>
+      <c r="L214" t="s">
+        <v>403</v>
+      </c>
+      <c r="M214" t="s">
+        <v>18</v>
+      </c>
+      <c r="N214" t="s">
+        <v>19</v>
+      </c>
+      <c r="O214" t="s">
+        <v>20</v>
+      </c>
+      <c r="P214" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>357</v>
+      </c>
+      <c r="R214" t="s">
+        <v>531</v>
+      </c>
+      <c r="S214">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>206</v>
+      </c>
+      <c r="B215" t="s">
+        <v>207</v>
+      </c>
+      <c r="C215" t="s">
+        <v>215</v>
+      </c>
+      <c r="D215" t="s">
+        <v>216</v>
+      </c>
+      <c r="E215" t="s">
+        <v>32</v>
+      </c>
+      <c r="F215" t="s">
+        <v>33</v>
+      </c>
+      <c r="G215" t="s">
+        <v>407</v>
+      </c>
+      <c r="H215" t="s">
+        <v>92</v>
+      </c>
+      <c r="I215" t="s">
+        <v>93</v>
+      </c>
+      <c r="J215">
+        <v>14.55</v>
+      </c>
+      <c r="K215" t="s">
+        <v>23</v>
+      </c>
+      <c r="L215" t="s">
+        <v>403</v>
+      </c>
+      <c r="M215" t="s">
+        <v>18</v>
+      </c>
+      <c r="N215" t="s">
+        <v>19</v>
+      </c>
+      <c r="O215" t="s">
+        <v>20</v>
+      </c>
+      <c r="P215" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>487</v>
+      </c>
+      <c r="R215" t="s">
+        <v>531</v>
+      </c>
+      <c r="S215">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>206</v>
+      </c>
+      <c r="B216" t="s">
+        <v>207</v>
+      </c>
+      <c r="C216" t="s">
+        <v>208</v>
+      </c>
+      <c r="D216" t="s">
+        <v>209</v>
+      </c>
+      <c r="E216" t="s">
+        <v>210</v>
+      </c>
+      <c r="F216" t="s">
+        <v>118</v>
+      </c>
+      <c r="G216" t="s">
+        <v>419</v>
+      </c>
+      <c r="H216" t="s">
+        <v>92</v>
+      </c>
+      <c r="I216" t="s">
+        <v>93</v>
+      </c>
+      <c r="J216">
+        <v>14.55</v>
+      </c>
+      <c r="K216" t="s">
+        <v>23</v>
+      </c>
+      <c r="L216" t="s">
+        <v>403</v>
+      </c>
+      <c r="M216" t="s">
+        <v>18</v>
+      </c>
+      <c r="N216" t="s">
+        <v>19</v>
+      </c>
+      <c r="O216" t="s">
+        <v>20</v>
+      </c>
+      <c r="P216" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>487</v>
+      </c>
+      <c r="R216" t="s">
+        <v>531</v>
+      </c>
+      <c r="S216">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>206</v>
+      </c>
+      <c r="B217" t="s">
+        <v>207</v>
+      </c>
+      <c r="C217" t="s">
+        <v>215</v>
+      </c>
+      <c r="D217" t="s">
+        <v>216</v>
+      </c>
+      <c r="E217" t="s">
+        <v>32</v>
+      </c>
+      <c r="F217" t="s">
+        <v>33</v>
+      </c>
+      <c r="G217" t="s">
+        <v>407</v>
+      </c>
+      <c r="H217" t="s">
+        <v>43</v>
+      </c>
+      <c r="I217" t="s">
+        <v>44</v>
+      </c>
+      <c r="J217">
+        <v>14.77</v>
+      </c>
+      <c r="K217" t="s">
+        <v>23</v>
+      </c>
+      <c r="L217" t="s">
+        <v>403</v>
+      </c>
+      <c r="M217" t="s">
+        <v>18</v>
+      </c>
+      <c r="N217" t="s">
+        <v>19</v>
+      </c>
+      <c r="O217" t="s">
+        <v>20</v>
+      </c>
+      <c r="P217" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>488</v>
+      </c>
+      <c r="R217" t="s">
+        <v>531</v>
+      </c>
+      <c r="S217">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>206</v>
+      </c>
+      <c r="B218" t="s">
+        <v>207</v>
+      </c>
+      <c r="C218" t="s">
+        <v>251</v>
+      </c>
+      <c r="D218" t="s">
+        <v>252</v>
+      </c>
+      <c r="E218" t="s">
+        <v>198</v>
+      </c>
+      <c r="F218" t="s">
+        <v>119</v>
+      </c>
+      <c r="G218" t="s">
+        <v>430</v>
+      </c>
+      <c r="H218" t="s">
+        <v>43</v>
+      </c>
+      <c r="I218" t="s">
+        <v>44</v>
+      </c>
+      <c r="J218">
+        <v>14.77</v>
+      </c>
+      <c r="K218" t="s">
+        <v>23</v>
+      </c>
+      <c r="L218" t="s">
+        <v>403</v>
+      </c>
+      <c r="M218" t="s">
+        <v>18</v>
+      </c>
+      <c r="N218" t="s">
+        <v>19</v>
+      </c>
+      <c r="O218" t="s">
+        <v>20</v>
+      </c>
+      <c r="P218" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>488</v>
+      </c>
+      <c r="R218" t="s">
+        <v>531</v>
+      </c>
+      <c r="S218">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>206</v>
+      </c>
+      <c r="B219" t="s">
+        <v>207</v>
+      </c>
+      <c r="C219" t="s">
+        <v>233</v>
+      </c>
+      <c r="D219" t="s">
+        <v>222</v>
+      </c>
+      <c r="E219" t="s">
+        <v>234</v>
+      </c>
+      <c r="F219" t="s">
+        <v>110</v>
+      </c>
+      <c r="G219" t="s">
+        <v>429</v>
+      </c>
+      <c r="H219" t="s">
+        <v>43</v>
+      </c>
+      <c r="I219" t="s">
+        <v>44</v>
+      </c>
+      <c r="J219">
+        <v>14.77</v>
+      </c>
+      <c r="K219" t="s">
+        <v>23</v>
+      </c>
+      <c r="L219" t="s">
+        <v>403</v>
+      </c>
+      <c r="M219" t="s">
+        <v>18</v>
+      </c>
+      <c r="N219" t="s">
+        <v>19</v>
+      </c>
+      <c r="O219" t="s">
+        <v>20</v>
+      </c>
+      <c r="P219" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>488</v>
+      </c>
+      <c r="R219" t="s">
+        <v>531</v>
+      </c>
+      <c r="S219">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>206</v>
+      </c>
+      <c r="B220" t="s">
+        <v>207</v>
+      </c>
+      <c r="C220" t="s">
+        <v>215</v>
+      </c>
+      <c r="D220" t="s">
+        <v>216</v>
+      </c>
+      <c r="E220" t="s">
+        <v>32</v>
+      </c>
+      <c r="F220" t="s">
+        <v>33</v>
+      </c>
+      <c r="G220" t="s">
+        <v>407</v>
+      </c>
+      <c r="H220" t="s">
+        <v>489</v>
+      </c>
+      <c r="I220" t="s">
+        <v>490</v>
+      </c>
+      <c r="J220">
+        <v>57.6</v>
+      </c>
+      <c r="K220" t="s">
+        <v>22</v>
+      </c>
+      <c r="L220" t="s">
+        <v>403</v>
+      </c>
+      <c r="M220" t="s">
+        <v>18</v>
+      </c>
+      <c r="N220" t="s">
+        <v>19</v>
+      </c>
+      <c r="O220" t="s">
+        <v>20</v>
+      </c>
+      <c r="P220" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>492</v>
+      </c>
+      <c r="R220" t="s">
+        <v>531</v>
+      </c>
+      <c r="S220">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>206</v>
+      </c>
+      <c r="B221" t="s">
+        <v>207</v>
+      </c>
+      <c r="C221" t="s">
+        <v>212</v>
+      </c>
+      <c r="D221" t="s">
+        <v>213</v>
+      </c>
+      <c r="E221" t="s">
+        <v>214</v>
+      </c>
+      <c r="F221" t="s">
+        <v>70</v>
+      </c>
+      <c r="G221" t="s">
+        <v>402</v>
+      </c>
+      <c r="H221" t="s">
+        <v>489</v>
+      </c>
+      <c r="I221" t="s">
+        <v>490</v>
+      </c>
+      <c r="J221">
+        <v>28.8</v>
+      </c>
+      <c r="K221" t="s">
+        <v>23</v>
+      </c>
+      <c r="L221" t="s">
+        <v>403</v>
+      </c>
+      <c r="M221" t="s">
+        <v>18</v>
+      </c>
+      <c r="N221" t="s">
+        <v>19</v>
+      </c>
+      <c r="O221" t="s">
+        <v>20</v>
+      </c>
+      <c r="P221" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>492</v>
+      </c>
+      <c r="R221" t="s">
+        <v>531</v>
+      </c>
+      <c r="S221">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>206</v>
+      </c>
+      <c r="B222" t="s">
+        <v>207</v>
+      </c>
+      <c r="C222" t="s">
+        <v>251</v>
+      </c>
+      <c r="D222" t="s">
+        <v>252</v>
+      </c>
+      <c r="E222" t="s">
+        <v>198</v>
+      </c>
+      <c r="F222" t="s">
+        <v>119</v>
+      </c>
+      <c r="G222" t="s">
+        <v>405</v>
+      </c>
+      <c r="H222" t="s">
+        <v>493</v>
+      </c>
+      <c r="I222" t="s">
+        <v>494</v>
+      </c>
+      <c r="J222">
+        <v>20.45</v>
+      </c>
+      <c r="K222" t="s">
+        <v>23</v>
+      </c>
+      <c r="L222" t="s">
+        <v>403</v>
+      </c>
+      <c r="M222" t="s">
+        <v>18</v>
+      </c>
+      <c r="N222" t="s">
+        <v>19</v>
+      </c>
+      <c r="O222" t="s">
+        <v>20</v>
+      </c>
+      <c r="P222" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>496</v>
+      </c>
+      <c r="R222" t="s">
+        <v>531</v>
+      </c>
+      <c r="S222">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>206</v>
+      </c>
+      <c r="B223" t="s">
+        <v>207</v>
+      </c>
+      <c r="C223" t="s">
+        <v>212</v>
+      </c>
+      <c r="D223" t="s">
+        <v>213</v>
+      </c>
+      <c r="E223" t="s">
+        <v>214</v>
+      </c>
+      <c r="F223" t="s">
+        <v>70</v>
+      </c>
+      <c r="G223" t="s">
+        <v>402</v>
+      </c>
+      <c r="H223" t="s">
+        <v>112</v>
+      </c>
+      <c r="I223" t="s">
+        <v>113</v>
+      </c>
+      <c r="J223">
+        <v>27.77</v>
+      </c>
+      <c r="K223" t="s">
+        <v>23</v>
+      </c>
+      <c r="L223" t="s">
+        <v>403</v>
+      </c>
+      <c r="M223" t="s">
+        <v>18</v>
+      </c>
+      <c r="N223" t="s">
+        <v>19</v>
+      </c>
+      <c r="O223" t="s">
+        <v>20</v>
+      </c>
+      <c r="P223" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>497</v>
+      </c>
+      <c r="R223" t="s">
+        <v>531</v>
+      </c>
+      <c r="S223">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>206</v>
+      </c>
+      <c r="B224" t="s">
+        <v>207</v>
+      </c>
+      <c r="C224" t="s">
+        <v>251</v>
+      </c>
+      <c r="D224" t="s">
+        <v>252</v>
+      </c>
+      <c r="E224" t="s">
+        <v>198</v>
+      </c>
+      <c r="F224" t="s">
+        <v>119</v>
+      </c>
+      <c r="G224" t="s">
+        <v>405</v>
+      </c>
+      <c r="H224" t="s">
+        <v>156</v>
+      </c>
+      <c r="I224" t="s">
+        <v>157</v>
+      </c>
+      <c r="J224">
+        <v>27.65</v>
+      </c>
+      <c r="K224" t="s">
+        <v>23</v>
+      </c>
+      <c r="L224" t="s">
+        <v>403</v>
+      </c>
+      <c r="M224" t="s">
+        <v>18</v>
+      </c>
+      <c r="N224" t="s">
+        <v>19</v>
+      </c>
+      <c r="O224" t="s">
+        <v>20</v>
+      </c>
+      <c r="P224" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>498</v>
+      </c>
+      <c r="R224" t="s">
+        <v>531</v>
+      </c>
+      <c r="S224">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="225" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>206</v>
+      </c>
+      <c r="B225" t="s">
+        <v>207</v>
+      </c>
+      <c r="C225" t="s">
+        <v>212</v>
+      </c>
+      <c r="D225" t="s">
+        <v>213</v>
+      </c>
+      <c r="E225" t="s">
+        <v>214</v>
+      </c>
+      <c r="F225" t="s">
+        <v>70</v>
+      </c>
+      <c r="G225" t="s">
+        <v>402</v>
+      </c>
+      <c r="H225" t="s">
+        <v>156</v>
+      </c>
+      <c r="I225" t="s">
+        <v>157</v>
+      </c>
+      <c r="J225">
+        <v>27.65</v>
+      </c>
+      <c r="K225" t="s">
+        <v>23</v>
+      </c>
+      <c r="L225" t="s">
+        <v>403</v>
+      </c>
+      <c r="M225" t="s">
+        <v>18</v>
+      </c>
+      <c r="N225" t="s">
+        <v>19</v>
+      </c>
+      <c r="O225" t="s">
+        <v>20</v>
+      </c>
+      <c r="P225" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>498</v>
+      </c>
+      <c r="R225" t="s">
+        <v>531</v>
+      </c>
+      <c r="S225">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="226" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>206</v>
+      </c>
+      <c r="B226" t="s">
+        <v>207</v>
+      </c>
+      <c r="C226" t="s">
+        <v>212</v>
+      </c>
+      <c r="D226" t="s">
+        <v>213</v>
+      </c>
+      <c r="E226" t="s">
+        <v>214</v>
+      </c>
+      <c r="F226" t="s">
+        <v>70</v>
+      </c>
+      <c r="G226" t="s">
+        <v>402</v>
+      </c>
+      <c r="H226" t="s">
+        <v>123</v>
+      </c>
+      <c r="I226" t="s">
+        <v>124</v>
+      </c>
+      <c r="J226">
+        <v>27.74</v>
+      </c>
+      <c r="K226" t="s">
+        <v>23</v>
+      </c>
+      <c r="L226" t="s">
+        <v>403</v>
+      </c>
+      <c r="M226" t="s">
+        <v>18</v>
+      </c>
+      <c r="N226" t="s">
+        <v>19</v>
+      </c>
+      <c r="O226" t="s">
+        <v>20</v>
+      </c>
+      <c r="P226" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>499</v>
+      </c>
+      <c r="R226" t="s">
+        <v>531</v>
+      </c>
+      <c r="S226">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="227" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>206</v>
+      </c>
+      <c r="B227" t="s">
+        <v>207</v>
+      </c>
+      <c r="C227" t="s">
+        <v>208</v>
+      </c>
+      <c r="D227" t="s">
+        <v>209</v>
+      </c>
+      <c r="E227" t="s">
+        <v>210</v>
+      </c>
+      <c r="F227" t="s">
+        <v>118</v>
+      </c>
+      <c r="G227" t="s">
+        <v>419</v>
+      </c>
+      <c r="H227" t="s">
+        <v>159</v>
+      </c>
+      <c r="I227" t="s">
+        <v>160</v>
+      </c>
+      <c r="J227">
+        <v>27.66</v>
+      </c>
+      <c r="K227" t="s">
+        <v>23</v>
+      </c>
+      <c r="L227" t="s">
+        <v>403</v>
+      </c>
+      <c r="M227" t="s">
+        <v>18</v>
+      </c>
+      <c r="N227" t="s">
+        <v>19</v>
+      </c>
+      <c r="O227" t="s">
+        <v>20</v>
+      </c>
+      <c r="P227" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>500</v>
+      </c>
+      <c r="R227" t="s">
+        <v>531</v>
+      </c>
+      <c r="S227">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="228" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>206</v>
+      </c>
+      <c r="B228" t="s">
+        <v>207</v>
+      </c>
+      <c r="C228" t="s">
+        <v>212</v>
+      </c>
+      <c r="D228" t="s">
+        <v>213</v>
+      </c>
+      <c r="E228" t="s">
+        <v>214</v>
+      </c>
+      <c r="F228" t="s">
+        <v>70</v>
+      </c>
+      <c r="G228" t="s">
+        <v>402</v>
+      </c>
+      <c r="H228" t="s">
+        <v>138</v>
+      </c>
+      <c r="I228" t="s">
+        <v>139</v>
+      </c>
+      <c r="J228">
+        <v>27.66</v>
+      </c>
+      <c r="K228" t="s">
+        <v>23</v>
+      </c>
+      <c r="L228" t="s">
+        <v>403</v>
+      </c>
+      <c r="M228" t="s">
+        <v>18</v>
+      </c>
+      <c r="N228" t="s">
+        <v>19</v>
+      </c>
+      <c r="O228" t="s">
+        <v>20</v>
+      </c>
+      <c r="P228" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>500</v>
+      </c>
+      <c r="R228" t="s">
+        <v>531</v>
+      </c>
+      <c r="S228">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="229" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>206</v>
+      </c>
+      <c r="B229" t="s">
+        <v>207</v>
+      </c>
+      <c r="C229" t="s">
+        <v>215</v>
+      </c>
+      <c r="D229" t="s">
+        <v>216</v>
+      </c>
+      <c r="E229" t="s">
+        <v>32</v>
+      </c>
+      <c r="F229" t="s">
+        <v>33</v>
+      </c>
+      <c r="G229" t="s">
+        <v>407</v>
+      </c>
+      <c r="H229" t="s">
+        <v>126</v>
+      </c>
+      <c r="I229" t="s">
+        <v>127</v>
+      </c>
+      <c r="J229">
+        <v>27.58</v>
+      </c>
+      <c r="K229" t="s">
+        <v>23</v>
+      </c>
+      <c r="L229" t="s">
+        <v>403</v>
+      </c>
+      <c r="M229" t="s">
+        <v>18</v>
+      </c>
+      <c r="N229" t="s">
+        <v>19</v>
+      </c>
+      <c r="O229" t="s">
+        <v>20</v>
+      </c>
+      <c r="P229" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>501</v>
+      </c>
+      <c r="R229" t="s">
+        <v>531</v>
+      </c>
+      <c r="S229">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="230" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>206</v>
+      </c>
+      <c r="B230" t="s">
+        <v>207</v>
+      </c>
+      <c r="C230" t="s">
+        <v>251</v>
+      </c>
+      <c r="D230" t="s">
+        <v>252</v>
+      </c>
+      <c r="E230" t="s">
+        <v>198</v>
+      </c>
+      <c r="F230" t="s">
+        <v>119</v>
+      </c>
+      <c r="G230" t="s">
+        <v>405</v>
+      </c>
+      <c r="H230" t="s">
+        <v>126</v>
+      </c>
+      <c r="I230" t="s">
+        <v>127</v>
+      </c>
+      <c r="J230">
+        <v>27.58</v>
+      </c>
+      <c r="K230" t="s">
+        <v>23</v>
+      </c>
+      <c r="L230" t="s">
+        <v>403</v>
+      </c>
+      <c r="M230" t="s">
+        <v>18</v>
+      </c>
+      <c r="N230" t="s">
+        <v>19</v>
+      </c>
+      <c r="O230" t="s">
+        <v>20</v>
+      </c>
+      <c r="P230" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>501</v>
+      </c>
+      <c r="R230" t="s">
+        <v>531</v>
+      </c>
+      <c r="S230">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="231" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>206</v>
+      </c>
+      <c r="B231" t="s">
+        <v>207</v>
+      </c>
+      <c r="C231" t="s">
+        <v>251</v>
+      </c>
+      <c r="D231" t="s">
+        <v>252</v>
+      </c>
+      <c r="E231" t="s">
+        <v>198</v>
+      </c>
+      <c r="F231" t="s">
+        <v>119</v>
+      </c>
+      <c r="G231" t="s">
+        <v>405</v>
+      </c>
+      <c r="H231" t="s">
+        <v>120</v>
+      </c>
+      <c r="I231" t="s">
+        <v>121</v>
+      </c>
+      <c r="J231">
+        <v>27.63</v>
+      </c>
+      <c r="K231" t="s">
+        <v>23</v>
+      </c>
+      <c r="L231" t="s">
+        <v>403</v>
+      </c>
+      <c r="M231" t="s">
+        <v>18</v>
+      </c>
+      <c r="N231" t="s">
+        <v>19</v>
+      </c>
+      <c r="O231" t="s">
+        <v>20</v>
+      </c>
+      <c r="P231" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>502</v>
+      </c>
+      <c r="R231" t="s">
+        <v>531</v>
+      </c>
+      <c r="S231">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="232" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>206</v>
+      </c>
+      <c r="B232" t="s">
+        <v>207</v>
+      </c>
+      <c r="C232" t="s">
+        <v>233</v>
+      </c>
+      <c r="D232" t="s">
+        <v>222</v>
+      </c>
+      <c r="E232" t="s">
+        <v>234</v>
+      </c>
+      <c r="F232" t="s">
+        <v>110</v>
+      </c>
+      <c r="G232" t="s">
+        <v>429</v>
+      </c>
+      <c r="H232" t="s">
+        <v>120</v>
+      </c>
+      <c r="I232" t="s">
+        <v>121</v>
+      </c>
+      <c r="J232">
+        <v>27.63</v>
+      </c>
+      <c r="K232" t="s">
+        <v>23</v>
+      </c>
+      <c r="L232" t="s">
+        <v>403</v>
+      </c>
+      <c r="M232" t="s">
+        <v>18</v>
+      </c>
+      <c r="N232" t="s">
+        <v>19</v>
+      </c>
+      <c r="O232" t="s">
+        <v>20</v>
+      </c>
+      <c r="P232" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>502</v>
+      </c>
+      <c r="R232" t="s">
+        <v>531</v>
+      </c>
+      <c r="S232">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="233" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>206</v>
+      </c>
+      <c r="B233" t="s">
+        <v>207</v>
+      </c>
+      <c r="C233" t="s">
+        <v>233</v>
+      </c>
+      <c r="D233" t="s">
+        <v>222</v>
+      </c>
+      <c r="E233" t="s">
+        <v>234</v>
+      </c>
+      <c r="F233" t="s">
+        <v>110</v>
+      </c>
+      <c r="G233" t="s">
+        <v>430</v>
+      </c>
+      <c r="H233" t="s">
+        <v>503</v>
+      </c>
+      <c r="I233" t="s">
+        <v>504</v>
+      </c>
+      <c r="J233">
+        <v>27.65</v>
+      </c>
+      <c r="K233" t="s">
+        <v>23</v>
+      </c>
+      <c r="L233" t="s">
+        <v>403</v>
+      </c>
+      <c r="M233" t="s">
+        <v>18</v>
+      </c>
+      <c r="N233" t="s">
+        <v>19</v>
+      </c>
+      <c r="O233" t="s">
+        <v>20</v>
+      </c>
+      <c r="P233" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>498</v>
+      </c>
+      <c r="R233" t="s">
+        <v>531</v>
+      </c>
+      <c r="S233">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="234" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>206</v>
+      </c>
+      <c r="B234" t="s">
+        <v>207</v>
+      </c>
+      <c r="C234" t="s">
+        <v>208</v>
+      </c>
+      <c r="D234" t="s">
+        <v>209</v>
+      </c>
+      <c r="E234" t="s">
+        <v>210</v>
+      </c>
+      <c r="F234" t="s">
+        <v>118</v>
+      </c>
+      <c r="G234" t="s">
+        <v>419</v>
+      </c>
+      <c r="H234" t="s">
+        <v>186</v>
+      </c>
+      <c r="I234" t="s">
+        <v>187</v>
+      </c>
+      <c r="J234">
+        <v>30.85</v>
+      </c>
+      <c r="K234" t="s">
+        <v>23</v>
+      </c>
+      <c r="L234" t="s">
+        <v>403</v>
+      </c>
+      <c r="M234" t="s">
+        <v>18</v>
+      </c>
+      <c r="N234" t="s">
+        <v>19</v>
+      </c>
+      <c r="O234" t="s">
+        <v>20</v>
+      </c>
+      <c r="P234" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>506</v>
+      </c>
+      <c r="R234" t="s">
+        <v>531</v>
+      </c>
+      <c r="S234">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>206</v>
+      </c>
+      <c r="B235" t="s">
+        <v>207</v>
+      </c>
+      <c r="C235" t="s">
+        <v>208</v>
+      </c>
+      <c r="D235" t="s">
+        <v>209</v>
+      </c>
+      <c r="E235" t="s">
+        <v>210</v>
+      </c>
+      <c r="F235" t="s">
+        <v>118</v>
+      </c>
+      <c r="G235" t="s">
+        <v>419</v>
+      </c>
+      <c r="H235" t="s">
+        <v>507</v>
+      </c>
+      <c r="I235" t="s">
+        <v>508</v>
+      </c>
+      <c r="J235">
+        <v>30.6</v>
+      </c>
+      <c r="K235" t="s">
+        <v>23</v>
+      </c>
+      <c r="L235" t="s">
+        <v>403</v>
+      </c>
+      <c r="M235" t="s">
+        <v>18</v>
+      </c>
+      <c r="N235" t="s">
+        <v>19</v>
+      </c>
+      <c r="O235" t="s">
+        <v>20</v>
+      </c>
+      <c r="P235" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>510</v>
+      </c>
+      <c r="R235" t="s">
+        <v>531</v>
+      </c>
+      <c r="S235">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>206</v>
+      </c>
+      <c r="B236" t="s">
+        <v>207</v>
+      </c>
+      <c r="C236" t="s">
+        <v>233</v>
+      </c>
+      <c r="D236" t="s">
+        <v>222</v>
+      </c>
+      <c r="E236" t="s">
+        <v>234</v>
+      </c>
+      <c r="F236" t="s">
+        <v>110</v>
+      </c>
+      <c r="G236" t="s">
+        <v>429</v>
+      </c>
+      <c r="H236" t="s">
+        <v>511</v>
+      </c>
+      <c r="I236" t="s">
+        <v>512</v>
+      </c>
+      <c r="J236">
+        <v>14.82</v>
+      </c>
+      <c r="K236" t="s">
+        <v>22</v>
+      </c>
+      <c r="L236" t="s">
+        <v>403</v>
+      </c>
+      <c r="M236" t="s">
+        <v>18</v>
+      </c>
+      <c r="N236" t="s">
+        <v>19</v>
+      </c>
+      <c r="O236" t="s">
+        <v>20</v>
+      </c>
+      <c r="P236" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>514</v>
+      </c>
+      <c r="R236" t="s">
+        <v>531</v>
+      </c>
+      <c r="S236">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>206</v>
+      </c>
+      <c r="B237" t="s">
+        <v>207</v>
+      </c>
+      <c r="C237" t="s">
+        <v>215</v>
+      </c>
+      <c r="D237" t="s">
+        <v>216</v>
+      </c>
+      <c r="E237" t="s">
+        <v>32</v>
+      </c>
+      <c r="F237" t="s">
+        <v>33</v>
+      </c>
+      <c r="G237" t="s">
+        <v>407</v>
+      </c>
+      <c r="H237" t="s">
+        <v>195</v>
+      </c>
+      <c r="I237" t="s">
+        <v>196</v>
+      </c>
+      <c r="J237">
+        <v>26.34</v>
+      </c>
+      <c r="K237" t="s">
+        <v>23</v>
+      </c>
+      <c r="L237" t="s">
+        <v>403</v>
+      </c>
+      <c r="M237" t="s">
+        <v>18</v>
+      </c>
+      <c r="N237" t="s">
+        <v>19</v>
+      </c>
+      <c r="O237" t="s">
+        <v>20</v>
+      </c>
+      <c r="P237" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>515</v>
+      </c>
+      <c r="R237" t="s">
+        <v>531</v>
+      </c>
+      <c r="S237">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>206</v>
+      </c>
+      <c r="B238" t="s">
+        <v>207</v>
+      </c>
+      <c r="C238" t="s">
+        <v>215</v>
+      </c>
+      <c r="D238" t="s">
+        <v>216</v>
+      </c>
+      <c r="E238" t="s">
+        <v>32</v>
+      </c>
+      <c r="F238" t="s">
+        <v>33</v>
+      </c>
+      <c r="G238" t="s">
+        <v>407</v>
+      </c>
+      <c r="H238" t="s">
+        <v>82</v>
+      </c>
+      <c r="I238" t="s">
+        <v>83</v>
+      </c>
+      <c r="J238">
+        <v>21.8</v>
+      </c>
+      <c r="K238" t="s">
+        <v>23</v>
+      </c>
+      <c r="L238" t="s">
+        <v>403</v>
+      </c>
+      <c r="M238" t="s">
+        <v>18</v>
+      </c>
+      <c r="N238" t="s">
+        <v>19</v>
+      </c>
+      <c r="O238" t="s">
+        <v>20</v>
+      </c>
+      <c r="P238" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>516</v>
+      </c>
+      <c r="R238" t="s">
+        <v>531</v>
+      </c>
+      <c r="S238">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>206</v>
+      </c>
+      <c r="B239" t="s">
+        <v>207</v>
+      </c>
+      <c r="C239" t="s">
+        <v>212</v>
+      </c>
+      <c r="D239" t="s">
+        <v>213</v>
+      </c>
+      <c r="E239" t="s">
+        <v>214</v>
+      </c>
+      <c r="F239" t="s">
+        <v>70</v>
+      </c>
+      <c r="G239" t="s">
+        <v>402</v>
+      </c>
+      <c r="H239" t="s">
+        <v>82</v>
+      </c>
+      <c r="I239" t="s">
+        <v>83</v>
+      </c>
+      <c r="J239">
+        <v>21.8</v>
+      </c>
+      <c r="K239" t="s">
+        <v>23</v>
+      </c>
+      <c r="L239" t="s">
+        <v>403</v>
+      </c>
+      <c r="M239" t="s">
+        <v>18</v>
+      </c>
+      <c r="N239" t="s">
+        <v>19</v>
+      </c>
+      <c r="O239" t="s">
+        <v>20</v>
+      </c>
+      <c r="P239" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>516</v>
+      </c>
+      <c r="R239" t="s">
+        <v>531</v>
+      </c>
+      <c r="S239">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>206</v>
+      </c>
+      <c r="B240" t="s">
+        <v>207</v>
+      </c>
+      <c r="C240" t="s">
+        <v>233</v>
+      </c>
+      <c r="D240" t="s">
+        <v>222</v>
+      </c>
+      <c r="E240" t="s">
+        <v>234</v>
+      </c>
+      <c r="F240" t="s">
+        <v>110</v>
+      </c>
+      <c r="G240" t="s">
+        <v>429</v>
+      </c>
+      <c r="H240" t="s">
+        <v>82</v>
+      </c>
+      <c r="I240" t="s">
+        <v>83</v>
+      </c>
+      <c r="J240">
+        <v>21.8</v>
+      </c>
+      <c r="K240" t="s">
+        <v>23</v>
+      </c>
+      <c r="L240" t="s">
+        <v>403</v>
+      </c>
+      <c r="M240" t="s">
+        <v>18</v>
+      </c>
+      <c r="N240" t="s">
+        <v>19</v>
+      </c>
+      <c r="O240" t="s">
+        <v>20</v>
+      </c>
+      <c r="P240" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>516</v>
+      </c>
+      <c r="R240" t="s">
+        <v>531</v>
+      </c>
+      <c r="S240">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>206</v>
+      </c>
+      <c r="B241" t="s">
+        <v>207</v>
+      </c>
+      <c r="C241" t="s">
+        <v>215</v>
+      </c>
+      <c r="D241" t="s">
+        <v>216</v>
+      </c>
+      <c r="E241" t="s">
+        <v>32</v>
+      </c>
+      <c r="F241" t="s">
+        <v>33</v>
+      </c>
+      <c r="G241" t="s">
+        <v>407</v>
+      </c>
+      <c r="H241" t="s">
+        <v>28</v>
+      </c>
+      <c r="I241" t="s">
+        <v>29</v>
+      </c>
+      <c r="J241">
+        <v>21.86</v>
+      </c>
+      <c r="K241" t="s">
+        <v>23</v>
+      </c>
+      <c r="L241" t="s">
+        <v>403</v>
+      </c>
+      <c r="M241" t="s">
+        <v>18</v>
+      </c>
+      <c r="N241" t="s">
+        <v>19</v>
+      </c>
+      <c r="O241" t="s">
+        <v>20</v>
+      </c>
+      <c r="P241" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>517</v>
+      </c>
+      <c r="R241" t="s">
+        <v>531</v>
+      </c>
+      <c r="S241">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>206</v>
+      </c>
+      <c r="B242" t="s">
+        <v>207</v>
+      </c>
+      <c r="C242" t="s">
+        <v>208</v>
+      </c>
+      <c r="D242" t="s">
+        <v>209</v>
+      </c>
+      <c r="E242" t="s">
+        <v>210</v>
+      </c>
+      <c r="F242" t="s">
+        <v>118</v>
+      </c>
+      <c r="G242" t="s">
+        <v>518</v>
+      </c>
+      <c r="H242" t="s">
+        <v>28</v>
+      </c>
+      <c r="I242" t="s">
+        <v>29</v>
+      </c>
+      <c r="J242">
+        <v>21.86</v>
+      </c>
+      <c r="K242" t="s">
+        <v>23</v>
+      </c>
+      <c r="L242" t="s">
+        <v>403</v>
+      </c>
+      <c r="M242" t="s">
+        <v>18</v>
+      </c>
+      <c r="N242" t="s">
+        <v>19</v>
+      </c>
+      <c r="O242" t="s">
+        <v>20</v>
+      </c>
+      <c r="P242" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>517</v>
+      </c>
+      <c r="R242" t="s">
+        <v>531</v>
+      </c>
+      <c r="S242">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>206</v>
+      </c>
+      <c r="B243" t="s">
+        <v>207</v>
+      </c>
+      <c r="C243" t="s">
+        <v>212</v>
+      </c>
+      <c r="D243" t="s">
+        <v>213</v>
+      </c>
+      <c r="E243" t="s">
+        <v>214</v>
+      </c>
+      <c r="F243" t="s">
+        <v>70</v>
+      </c>
+      <c r="G243" t="s">
+        <v>402</v>
+      </c>
+      <c r="H243" t="s">
+        <v>28</v>
+      </c>
+      <c r="I243" t="s">
+        <v>29</v>
+      </c>
+      <c r="J243">
+        <v>21.86</v>
+      </c>
+      <c r="K243" t="s">
+        <v>23</v>
+      </c>
+      <c r="L243" t="s">
+        <v>403</v>
+      </c>
+      <c r="M243" t="s">
+        <v>18</v>
+      </c>
+      <c r="N243" t="s">
+        <v>19</v>
+      </c>
+      <c r="O243" t="s">
+        <v>20</v>
+      </c>
+      <c r="P243" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>517</v>
+      </c>
+      <c r="R243" t="s">
+        <v>531</v>
+      </c>
+      <c r="S243">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>206</v>
+      </c>
+      <c r="B244" t="s">
+        <v>207</v>
+      </c>
+      <c r="C244" t="s">
+        <v>208</v>
+      </c>
+      <c r="D244" t="s">
+        <v>209</v>
+      </c>
+      <c r="E244" t="s">
+        <v>210</v>
+      </c>
+      <c r="F244" t="s">
+        <v>118</v>
+      </c>
+      <c r="G244" t="s">
+        <v>518</v>
+      </c>
+      <c r="H244" t="s">
+        <v>64</v>
+      </c>
+      <c r="I244" t="s">
+        <v>65</v>
+      </c>
+      <c r="J244">
+        <v>21.88</v>
+      </c>
+      <c r="K244" t="s">
+        <v>23</v>
+      </c>
+      <c r="L244" t="s">
+        <v>403</v>
+      </c>
+      <c r="M244" t="s">
+        <v>18</v>
+      </c>
+      <c r="N244" t="s">
+        <v>19</v>
+      </c>
+      <c r="O244" t="s">
+        <v>20</v>
+      </c>
+      <c r="P244" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>519</v>
+      </c>
+      <c r="R244" t="s">
+        <v>531</v>
+      </c>
+      <c r="S244">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="245" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>206</v>
+      </c>
+      <c r="B245" t="s">
+        <v>207</v>
+      </c>
+      <c r="C245" t="s">
+        <v>212</v>
+      </c>
+      <c r="D245" t="s">
+        <v>213</v>
+      </c>
+      <c r="E245" t="s">
+        <v>214</v>
+      </c>
+      <c r="F245" t="s">
+        <v>70</v>
+      </c>
+      <c r="G245" t="s">
+        <v>402</v>
+      </c>
+      <c r="H245" t="s">
+        <v>64</v>
+      </c>
+      <c r="I245" t="s">
+        <v>65</v>
+      </c>
+      <c r="J245">
+        <v>21.88</v>
+      </c>
+      <c r="K245" t="s">
+        <v>23</v>
+      </c>
+      <c r="L245" t="s">
+        <v>403</v>
+      </c>
+      <c r="M245" t="s">
+        <v>18</v>
+      </c>
+      <c r="N245" t="s">
+        <v>19</v>
+      </c>
+      <c r="O245" t="s">
+        <v>20</v>
+      </c>
+      <c r="P245" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>519</v>
+      </c>
+      <c r="R245" t="s">
+        <v>531</v>
+      </c>
+      <c r="S245">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="246" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>206</v>
+      </c>
+      <c r="B246" t="s">
+        <v>207</v>
+      </c>
+      <c r="C246" t="s">
+        <v>215</v>
+      </c>
+      <c r="D246" t="s">
+        <v>216</v>
+      </c>
+      <c r="E246" t="s">
+        <v>32</v>
+      </c>
+      <c r="F246" t="s">
+        <v>33</v>
+      </c>
+      <c r="G246" t="s">
+        <v>407</v>
+      </c>
+      <c r="H246" t="s">
+        <v>171</v>
+      </c>
+      <c r="I246" t="s">
+        <v>172</v>
+      </c>
+      <c r="J246">
+        <v>12.71</v>
+      </c>
+      <c r="K246" t="s">
+        <v>23</v>
+      </c>
+      <c r="L246" t="s">
+        <v>403</v>
+      </c>
+      <c r="M246" t="s">
+        <v>18</v>
+      </c>
+      <c r="N246" t="s">
+        <v>19</v>
+      </c>
+      <c r="O246" t="s">
+        <v>20</v>
+      </c>
+      <c r="P246" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>520</v>
+      </c>
+      <c r="R246" t="s">
+        <v>531</v>
+      </c>
+      <c r="S246">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="247" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>206</v>
+      </c>
+      <c r="B247" t="s">
+        <v>207</v>
+      </c>
+      <c r="C247" t="s">
+        <v>208</v>
+      </c>
+      <c r="D247" t="s">
+        <v>209</v>
+      </c>
+      <c r="E247" t="s">
+        <v>210</v>
+      </c>
+      <c r="F247" t="s">
+        <v>118</v>
+      </c>
+      <c r="G247" t="s">
+        <v>463</v>
+      </c>
+      <c r="H247" t="s">
+        <v>521</v>
+      </c>
+      <c r="I247" t="s">
+        <v>522</v>
+      </c>
+      <c r="J247">
+        <v>36.450000000000003</v>
+      </c>
+      <c r="K247" t="s">
+        <v>23</v>
+      </c>
+      <c r="L247" t="s">
+        <v>403</v>
+      </c>
+      <c r="M247" t="s">
+        <v>18</v>
+      </c>
+      <c r="N247" t="s">
+        <v>19</v>
+      </c>
+      <c r="O247" t="s">
+        <v>20</v>
+      </c>
+      <c r="P247" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>524</v>
+      </c>
+      <c r="R247" t="s">
+        <v>531</v>
+      </c>
+      <c r="S247">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="248" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>206</v>
+      </c>
+      <c r="B248" t="s">
+        <v>207</v>
+      </c>
+      <c r="C248" t="s">
+        <v>215</v>
+      </c>
+      <c r="D248" t="s">
+        <v>216</v>
+      </c>
+      <c r="E248" t="s">
+        <v>32</v>
+      </c>
+      <c r="F248" t="s">
+        <v>33</v>
+      </c>
+      <c r="G248" t="s">
+        <v>525</v>
+      </c>
+      <c r="H248" t="s">
+        <v>34</v>
+      </c>
+      <c r="I248" t="s">
+        <v>35</v>
+      </c>
+      <c r="J248">
+        <v>22.28</v>
+      </c>
+      <c r="K248" t="s">
+        <v>22</v>
+      </c>
+      <c r="L248" t="s">
+        <v>403</v>
+      </c>
+      <c r="M248" t="s">
+        <v>18</v>
+      </c>
+      <c r="N248" t="s">
+        <v>19</v>
+      </c>
+      <c r="O248" t="s">
+        <v>20</v>
+      </c>
+      <c r="P248" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>526</v>
+      </c>
+      <c r="R248" t="s">
+        <v>531</v>
+      </c>
+      <c r="S248">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="249" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>206</v>
+      </c>
+      <c r="B249" t="s">
+        <v>207</v>
+      </c>
+      <c r="C249" t="s">
+        <v>221</v>
+      </c>
+      <c r="D249" t="s">
+        <v>222</v>
+      </c>
+      <c r="E249" t="s">
+        <v>223</v>
+      </c>
+      <c r="F249" t="s">
+        <v>151</v>
+      </c>
+      <c r="G249" t="s">
+        <v>527</v>
+      </c>
+      <c r="H249" t="s">
+        <v>95</v>
+      </c>
+      <c r="I249" t="s">
+        <v>96</v>
+      </c>
+      <c r="J249">
+        <v>105</v>
+      </c>
+      <c r="K249" t="s">
+        <v>68</v>
+      </c>
+      <c r="L249" t="s">
+        <v>403</v>
+      </c>
+      <c r="M249" t="s">
+        <v>18</v>
+      </c>
+      <c r="N249" t="s">
+        <v>19</v>
+      </c>
+      <c r="O249" t="s">
+        <v>20</v>
+      </c>
+      <c r="P249" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>528</v>
+      </c>
+      <c r="R249" t="s">
+        <v>531</v>
+      </c>
+      <c r="S249">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="250" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>206</v>
+      </c>
+      <c r="B250" t="s">
+        <v>207</v>
+      </c>
+      <c r="C250" t="s">
+        <v>212</v>
+      </c>
+      <c r="D250" t="s">
+        <v>213</v>
+      </c>
+      <c r="E250" t="s">
+        <v>214</v>
+      </c>
+      <c r="F250" t="s">
+        <v>70</v>
+      </c>
+      <c r="G250" t="s">
+        <v>529</v>
+      </c>
+      <c r="H250" t="s">
+        <v>393</v>
+      </c>
+      <c r="I250" t="s">
+        <v>394</v>
+      </c>
+      <c r="J250">
+        <v>10.54</v>
+      </c>
+      <c r="K250" t="s">
+        <v>23</v>
+      </c>
+      <c r="L250" t="s">
+        <v>403</v>
+      </c>
+      <c r="M250" t="s">
+        <v>18</v>
+      </c>
+      <c r="N250" t="s">
+        <v>19</v>
+      </c>
+      <c r="O250" t="s">
+        <v>20</v>
+      </c>
+      <c r="P250" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>530</v>
+      </c>
+      <c r="R250" t="s">
+        <v>531</v>
+      </c>
+      <c r="S250">
         <v>2026</v>
       </c>
     </row>
@@ -10882,6 +16759,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007AF750F8789DE14FB4E04CAEE69C2EC6" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fa8363fe0f9a90aa18bd49cba0a1c92f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ffd56821-1536-474c-aeb3-bbda9de7a36b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7db7e2f66cb7e500deeedabc50b2c1b2" ns2:_="">
     <xsd:import namespace="ffd56821-1536-474c-aeb3-bbda9de7a36b"/>
@@ -11019,15 +16905,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -11035,6 +16912,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCE63C2-9EDB-4C06-BCC1-92BC6FE21478}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04413B18-401A-4E6E-BA96-19E21239F9CD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11052,14 +16937,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCE63C2-9EDB-4C06-BCC1-92BC6FE21478}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{572CA61F-FEEA-42AE-BDCD-4177C47A2D3E}">
   <ds:schemaRefs>
